--- a/seven-knights-counter-app/counter-template.xlsx
+++ b/seven-knights-counter-app/counter-template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="1" r:id="R9d7c673bdb054049"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="방어팀" sheetId="2" r:id="R56a6552933fe4321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공략덱" sheetId="3" r:id="R783ecab52a1b4319"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참조_영웅" sheetId="4" r:id="Rf89f6b2454314bda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="1" r:id="R060e4cfd04124a7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="방어팀" sheetId="2" r:id="R01a1a9e63f104d1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공략덱" sheetId="3" r:id="Rc21f2f97623f426c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참조_영웅" sheetId="4" r:id="R61c3347caa4f441a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -124,10 +124,13 @@
     <x:t xml:space="preserve">밀리아</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">yeopo-branz-bransel-pi</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">여란파</x:t>
@@ -136,8 +139,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">여포</x:t>
@@ -149,18 +152,21 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">파이</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">yeopo-branz-bransel-landgride</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">여쁘란</x:t>
@@ -169,18 +175,21 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">란드그리드</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">yeopo-branz-bransel-amelia</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">여쁘아</x:t>
@@ -189,16 +198,16 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">브란즈</x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
         <x:family val="2"/>
       </x:rPr>
@@ -206,8 +215,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">브란셀</x:t>
@@ -216,18 +225,21 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">아멜리아</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">tuto-gelidus-mist</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">트겔미</x:t>
@@ -236,8 +248,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">트루드</x:t>
@@ -246,8 +258,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">겔리두스</x:t>
@@ -256,18 +268,21 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">미스트</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">omok-freya-reginleif</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">오프레</x:t>
@@ -276,8 +291,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">오목</x:t>
@@ -289,18 +304,21 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">레긴레이프</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">milia-freya-vanessa</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">밀프바</x:t>
@@ -309,8 +327,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">밀리아</x:t>
@@ -319,28 +337,34 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">바네사</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">milia-freya-reginleif</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">밀프레</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">ludgride-son-ogong-ellisia</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">라오엘</x:t>
@@ -355,18 +379,21 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">엘리시아</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">ludgride-son-ogong-gelidus</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">라오겔</x:t>
@@ -375,8 +402,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">라드그리드</x:t>
@@ -385,18 +412,21 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">손오공</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">yeopo-landgride-karl-heron</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">여란칼</x:t>
@@ -405,16 +435,16 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">칼</x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
         <x:family val="2"/>
       </x:rPr>
@@ -422,18 +452,21 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">헤론</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">omok-choseon-run</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">오초린</x:t>
@@ -442,8 +475,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">초선</x:t>
@@ -452,14 +485,26 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="1100"/>
-        <x:color rgb="FF000000"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF111827"/>
         <x:rFont val="Carlito"/>
       </x:rPr>
       <x:t xml:space="preserve">린</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">pala-ara-ro</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">팔로아</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">팔라누스</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">아라곤</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">공략덱ID</x:t>
   </x:si>
   <x:si>
@@ -490,9 +535,6 @@
     <x:t xml:space="preserve">공략3영웅</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">진형설명</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">스킬순서</x:t>
   </x:si>
   <x:si>
@@ -515,9 +557,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">겔리두스</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">파이 후열, 겔리두스와 태오 전열 압박</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">파이 2스킬
@@ -547,9 +586,6 @@
     <x:t xml:space="preserve">밸런스 진형</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">로지 선턴, 파이 마무리, 클레미스 보조</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">로지 1스킬
 클레미스 2스킬
 파이 2스킬
@@ -571,9 +607,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">보호 진형</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">레이첼 후열, 클레미스와 밀리아 전열 유지</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">클레미스 2스킬
@@ -603,9 +636,6 @@
     <x:t xml:space="preserve">아일린</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">아일린 전열, 겔리두스 광역, 파이 후열</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">아일린 2스킬
 겔리두스 2스킬
 파이 2스킬
@@ -624,9 +654,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">태오 카일 연타</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">태오 후열, 카일 추격, 클레미스 보조</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">클레미스 2스킬
@@ -644,6 +671,523 @@
     <x:t xml:space="preserve">로지 침묵을 저항으로 받아내고 단일 타격으로 후열을 빠르게 정리합니다.</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">여쁘태</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여포</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태2 여1 여2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태오: 권능
+여포: 권능
+브브: 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">속공따야함</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">라오챈</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">챈슬러</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오2 챈2 오1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">5성이상 부활</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">내실</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여카쁘</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">카2 쁘1 여1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">카일: 권능
+여포: 권능
+브브: 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">챈2 오2 라1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">라트챈</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">트루드</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">라1 챈2 트2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">트루드: 권능
+5성이상 부활</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">라오트</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">라1 오2 트2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여태쁘</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태2 태1 여1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태2 여1 쁘1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태카란</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">란드그리드</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태2 카2 태1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태오: 권능
+카일: 권능
+란드: 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여쁘란</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여1 여2 쁘1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여포: 권능
+브브: 불사
+란드: 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여1 카2 쁘1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여포: 권능
+브브: 불사
+카일: 권능</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여태란</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태2 여1 태1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여포: 권능
+태오: 권능
+란드: 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">카태란</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">카일</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">: </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">권능
+태오</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">: </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">권능
+란드</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">: </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">불사</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">라오겔</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오2 겔1 오1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">밀프레</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">레긴레이프</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">밀2 프2 레2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">프레: 권능,불사
+레긴: 권능
+밀리아: 권능,불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">카파란</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">카1 란2 카2</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="11"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">카일</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="11"/>
+        <x:rFont val="Arial"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">: </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="11"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">권능
+파이</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="11"/>
+        <x:rFont val="Arial"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">: </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="11"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">불사</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="11"/>
+        <x:rFont val="Arial"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">,</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="11"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">권능
+란드: 불사</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">카2 란2 카1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">레멜린</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">멜키르</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">린</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">린2 멜2 레2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">레긴: 권능
+린: 권능, 불사
+멜: 권능, 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오프린</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오목</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오1 린2 프2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오목: 불사
+프레: 권능, 불사
+린: 권능, 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">밀오린</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">린2 오1 오2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">밀리아: 권능, 불사
+오목: 불사
+린: 권능, 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="11"/>
+        <x:rFont val="Malgun Gothic"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">여란</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="11"/>
+        <x:rFont val="Carlito"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">+@</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">공격형</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여1 여2 +@</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여포: 권능
+란드: 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="11"/>
+        <x:rFont val="Malgun Gothic"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">라오</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="11"/>
+        <x:rFont val="Carlito"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">+@</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">만능,지원</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오1 오2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">카란발</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">발리스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">카1 카2 발1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">카일: 불사, 권능
+란드: 불사
+발리: 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">속공,내실</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">플팔아</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">플라튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">팔라두스</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">아2 팔1 팔2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">프2 레2 밀2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">레긴: 권능
+프레: 권능, 불사
+밀리아: 권능, 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">레2 프2 레1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">프바레</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">바네사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">바1 프2 레2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">레긴: 권능
+프레: 권능, 불사
+바네: 권능, 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">미로아</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">아킬라</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">미스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">미2 미1 아2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">로지: 부활
+아킬라: 부활
+미스트: 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">속공150+ 내실</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">미로녹</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">녹스</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">미2 미1 녹2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">로지: 부활, 불사
+미스트: 불사
+녹스: 불사, 부활</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">속공200+ 내실</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">라오에</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">에이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오2 오1 에2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여란칼</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">칼 헤론</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여1 칼1 여2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여포: 불사, 권능
+란드: 불사
+칼: 불사, 권능</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">라1 챈2 오2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태칼쁘</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태2 태1 쁘1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태오: 권능
+칼: 권능, 불사
+브브: 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">상대보다 속공+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">플루엘</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">루디</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">엘리스</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">플2 엘2 루2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">효저세공 반지+ 셋다 효저 90이상 받받+ 막기 챙기기(조율자 필수)</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">영웅ID</x:t>
   </x:si>
   <x:si>
@@ -656,9 +1200,6 @@
     <x:t xml:space="preserve">pi</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">공격형</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">julie</x:t>
   </x:si>
   <x:si>
@@ -707,9 +1248,6 @@
     <x:t xml:space="preserve">platin</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">플라튼</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">kris</x:t>
   </x:si>
   <x:si>
@@ -746,15 +1284,9 @@
     <x:t xml:space="preserve">yeopo</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">여포</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">karl-heron</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">칼 헤론</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">yeonhee</x:t>
   </x:si>
   <x:si>
@@ -764,24 +1296,15 @@
     <x:t xml:space="preserve">vanessa</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">바네사</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">melkir</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">멜키르</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">freya</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">run</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">린</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">nata</x:t>
   </x:si>
   <x:si>
@@ -791,15 +1314,9 @@
     <x:t xml:space="preserve">omok</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">오목</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">rudy</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">루디</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">biscuit</x:t>
   </x:si>
   <x:si>
@@ -830,21 +1347,12 @@
     <x:t xml:space="preserve">tuto</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">트루드</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">palanus</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">팔라누스</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">landgride</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">란드그리드</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">sung-jinwoo</x:t>
   </x:si>
   <x:si>
@@ -854,15 +1362,9 @@
     <x:t xml:space="preserve">ace</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">에이스</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">mist</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">미스트</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">delons</x:t>
   </x:si>
   <x:si>
@@ -878,9 +1380,6 @@
     <x:t xml:space="preserve">reginleif</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">레긴레이프</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">skuld</x:t>
   </x:si>
   <x:si>
@@ -890,9 +1389,6 @@
     <x:t xml:space="preserve">aquila</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">아킬라</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">orly</x:t>
   </x:si>
   <x:si>
@@ -938,9 +1434,6 @@
     <x:t xml:space="preserve">blista</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">발리스타</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">taka</x:t>
   </x:si>
   <x:si>
@@ -956,9 +1449,6 @@
     <x:t xml:space="preserve">alice</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">엘리스</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">miho</x:t>
   </x:si>
   <x:si>
@@ -968,9 +1458,6 @@
     <x:t xml:space="preserve">aragon</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">아라곤</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">guan-yu</x:t>
   </x:si>
   <x:si>
@@ -1016,9 +1503,6 @@
     <x:t xml:space="preserve">nox</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">녹스</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">rook</x:t>
   </x:si>
   <x:si>
@@ -1044,9 +1528,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">chancellor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">챈슬러</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">baka</x:t>
@@ -1269,7 +1750,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="17">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -1301,15 +1782,59 @@
       <x:name val="돋움"/>
     </x:font>
     <x:font>
+      <x:b/>
       <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF111827"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:sz val="11"/>
       <x:name val="맑은 고딕"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1331,8 +1856,28 @@
         <x:fgColor rgb="FF111827"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF111827"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF111827"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="17">
+  <x:borders count="23">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -1438,12 +1983,72 @@
         <x:color rgb="FFCBD5E1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E1EA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E1EA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E1EA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E1EA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E1EA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD9E1EA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E1EA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E1EA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E1EA"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1480,18 +2085,57 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -1544,9 +2188,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1702,14 +2346,14 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="20.25">
-      <x:c r="A1" s="18" t="s">
+      <x:c r="A1" s="31" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="18"/>
-      <x:c r="C1" s="18"/>
-      <x:c r="D1" s="18"/>
-      <x:c r="E1" s="18"/>
-      <x:c r="F1" s="18"/>
+      <x:c r="B1" s="31"/>
+      <x:c r="C1" s="31"/>
+      <x:c r="D1" s="31"/>
+      <x:c r="E1" s="31"/>
+      <x:c r="F1" s="31"/>
     </x:row>
     <x:row r="3" ht="15">
       <x:c r="A3" s="1" t="s">
@@ -1790,319 +2434,388 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" customWidth="1"/>
     <x:col min="2" max="2" width="24" customWidth="1"/>
-    <x:col min="3" max="6" width="16" customWidth="1"/>
-    <x:col min="7" max="7" width="48" customWidth="1"/>
+    <x:col min="3" max="5" width="18" customWidth="1"/>
+    <x:col min="6" max="6" width="10" customWidth="1"/>
+    <x:col min="7" max="7" width="52" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15">
-      <x:c r="A1" s="9" t="s">
+    <x:row r="1" ht="21.950000762939453" customHeight="1">
+      <x:c r="A1" s="18" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="19" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s">
+      <x:c r="C1" s="19" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D1" s="10" t="s">
+      <x:c r="D1" s="19" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E1" s="10" t="s">
+      <x:c r="E1" s="19" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F1" s="10" t="s">
+      <x:c r="F1" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G1" s="11" t="s">
+      <x:c r="G1" s="20" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="12" t="s">
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" s="21" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B2" s="13" t="s">
+      <x:c r="B2" s="22" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C2" s="13" t="s">
+      <x:c r="C2" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D2" s="13" t="s">
+      <x:c r="D2" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E2" s="13" t="s">
+      <x:c r="E2" s="22" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F2" s="13" t="s">
+      <x:c r="F2" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G2" s="14" t="s">
+      <x:c r="G2" s="23" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="12" t="s">
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" s="21" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="s">
+      <x:c r="B3" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C3" s="13" t="s">
+      <x:c r="C3" s="22" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D3" s="13" t="s">
+      <x:c r="D3" s="22" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="s">
+      <x:c r="E3" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="s">
+      <x:c r="F3" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G3" s="14"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="15" t="s">
+      <x:c r="G3" s="23"/>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" s="21" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="s">
+      <x:c r="B4" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C4" s="16" t="s">
+      <x:c r="C4" s="22" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="s">
+      <x:c r="D4" s="22" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="s">
+      <x:c r="E4" s="22" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F4" s="16" t="s">
+      <x:c r="F4" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G4" s="17"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>yeopo-branz-bransel-pi</x:v>
-      </x:c>
-      <x:c r="B5" s="19" t="s">
+      <x:c r="G4" s="23"/>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" s="21" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C5" s="19" t="s">
+      <x:c r="B5" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D5" s="13" t="s">
+      <x:c r="C5" s="22" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E5" s="19" t="s">
+      <x:c r="D5" s="22" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F5" s="16" t="s">
+      <x:c r="E5" s="22" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>yeopo-branz-bransel-landgride</x:v>
-      </x:c>
-      <x:c r="B6" s="19" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C6" s="19" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D6" s="13" t="s">
+      <x:c r="G5" s="22"/>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" s="21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B6" s="22" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C6" s="22" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E6" s="19" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F6" s="16" t="s">
+      <x:c r="D6" s="22" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E6" s="22" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F6" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>yeopo-branz-bransel-amelia</x:v>
-      </x:c>
-      <x:c r="B7" s="19" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C7" s="19" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D7" s="20" t="s">
+      <x:c r="G6" s="22"/>
+    </x:row>
+    <x:row r="7" ht="21" customHeight="1">
+      <x:c r="A7" s="21" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B7" s="22" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C7" s="22" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D7" s="22" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E7" s="22" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F7" s="22" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G7" s="22"/>
+    </x:row>
+    <x:row r="8" ht="21" customHeight="1">
+      <x:c r="A8" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B8" s="22" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C8" s="22" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D8" s="22" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E8" s="22" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F8" s="22" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G8" s="22"/>
+    </x:row>
+    <x:row r="9" ht="21" customHeight="1">
+      <x:c r="A9" s="21" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F9" s="22" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G9" s="22"/>
+    </x:row>
+    <x:row r="10" ht="21" customHeight="1">
+      <x:c r="A10" s="21" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F10" s="22" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="22"/>
+    </x:row>
+    <x:row r="11" ht="21" customHeight="1">
+      <x:c r="A11" s="21" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F11" s="22" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G11" s="22"/>
+    </x:row>
+    <x:row r="12" ht="21" customHeight="1">
+      <x:c r="A12" s="21" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F12" s="22" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G12" s="22"/>
+    </x:row>
+    <x:row r="13" ht="21" customHeight="1">
+      <x:c r="A13" s="21" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D13" s="22" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F13" s="22" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G13" s="22"/>
+    </x:row>
+    <x:row r="14" ht="21" customHeight="1">
+      <x:c r="A14" s="21" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D14" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E7" s="19" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="E14" s="22" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F14" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>tuto-gelidus-mist</x:v>
-      </x:c>
-      <x:c r="B8" s="19" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D8" s="20" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F8" s="16" t="s">
+      <x:c r="G14" s="22"/>
+    </x:row>
+    <x:row r="15" ht="21" customHeight="1">
+      <x:c r="A15" s="21" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D15" s="22" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F15" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>omok-freya-reginleif</x:v>
-      </x:c>
-      <x:c r="B9" s="19" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D9" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F9" s="16" t="s">
+      <x:c r="G15" s="22"/>
+    </x:row>
+    <x:row r="16" ht="21" customHeight="1">
+      <x:c r="A16" s="21" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D16" s="22" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E16" s="22" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F16" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>milia-freya-vanessa</x:v>
-      </x:c>
-      <x:c r="B10" s="19" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D10" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>milia-freya-reginleif</x:v>
-      </x:c>
-      <x:c r="B11" s="19" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E11" s="19" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="16.5">
-      <x:c r="A12" t="str">
-        <x:v>ludgride-son-ogong-ellisia</x:v>
-      </x:c>
-      <x:c r="B12" s="19" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D12" s="21" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E12" s="19" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>ludgride-son-ogong-gelidus</x:v>
-      </x:c>
-      <x:c r="B13" s="19" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C13" s="19" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D13" s="20" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E13" s="19" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>yeopo-landgride-karl-heron</x:v>
-      </x:c>
-      <x:c r="B14" s="19" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D14" s="20" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E14" s="19" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>omok-choseon-run</x:v>
-      </x:c>
-      <x:c r="B15" s="19" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C15" s="19" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D15" s="20" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E15" s="19" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
+      <x:c r="G16" s="22"/>
+    </x:row>
+    <x:row r="17" ht="21" customHeight="1">
+      <x:c r="A17" s="21"/>
+      <x:c r="B17" s="22"/>
+      <x:c r="C17" s="22"/>
+      <x:c r="D17" s="22"/>
+      <x:c r="E17" s="22"/>
+      <x:c r="F17" s="22"/>
+      <x:c r="G17" s="22"/>
+    </x:row>
+    <x:row r="18" ht="21" customHeight="1">
+      <x:c r="A18" s="21"/>
+      <x:c r="B18" s="22"/>
+      <x:c r="C18" s="22"/>
+      <x:c r="D18" s="22"/>
+      <x:c r="E18" s="22"/>
+      <x:c r="F18" s="22"/>
+      <x:c r="G18" s="22"/>
+    </x:row>
+    <x:row r="19" ht="21" customHeight="1">
+      <x:c r="A19" s="21"/>
+      <x:c r="B19" s="22"/>
+      <x:c r="C19" s="22"/>
+      <x:c r="D19" s="22"/>
+      <x:c r="E19" s="22"/>
+      <x:c r="F19" s="22"/>
+      <x:c r="G19" s="22"/>
+    </x:row>
+    <x:row r="20" ht="21" customHeight="1">
+      <x:c r="A20" s="21"/>
+      <x:c r="B20" s="22"/>
+      <x:c r="C20" s="22"/>
+      <x:c r="D20" s="22"/>
+      <x:c r="E20" s="22"/>
+      <x:c r="F20" s="22"/>
+      <x:c r="G20" s="22"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2113,313 +2826,2105 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14.25"/>
   <x:cols>
-    <x:col min="1" max="2" width="14" customWidth="1"/>
-    <x:col min="3" max="3" width="22" customWidth="1"/>
-    <x:col min="4" max="11" width="14" customWidth="1"/>
-    <x:col min="12" max="14" width="42" customWidth="1"/>
-    <x:col min="15" max="15" width="14" customWidth="1"/>
-    <x:col min="16" max="16" width="54" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="3" width="22" customWidth="1"/>
+    <x:col min="4" max="4" width="10" customWidth="1"/>
+    <x:col min="5" max="5" width="14" customWidth="1"/>
+    <x:col min="6" max="6" width="10" customWidth="1"/>
+    <x:col min="7" max="7" width="14" customWidth="1"/>
+    <x:col min="8" max="8" width="10" customWidth="1"/>
+    <x:col min="9" max="9" width="14" customWidth="1"/>
+    <x:col min="10" max="10" width="10" customWidth="1"/>
+    <x:col min="11" max="11" width="14" customWidth="1"/>
+    <x:col min="12" max="12" width="34" customWidth="1"/>
+    <x:col min="13" max="13" width="38" customWidth="1"/>
+    <x:col min="14" max="14" width="10" customWidth="1"/>
+    <x:col min="15" max="15" width="52" customWidth="1"/>
+    <x:col min="16" max="16" width="2" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15">
-      <x:c r="A1" s="9" t="s">
+    <x:row r="1" ht="21.950000762939453" customHeight="1">
+      <x:c r="A1" s="28" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="29" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C1" s="29" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D1" s="29" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E1" s="29" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F1" s="29" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G1" s="29" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H1" s="29" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="I1" s="29" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="J1" s="29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="K1" s="29" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="L1" s="29" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="M1" s="29" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="N1" s="29" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="O1" s="29" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P1" s="30"/>
+      <x:c r="Q1" s="29"/>
+      <x:c r="R1" s="29"/>
+      <x:c r="S1" s="29"/>
+      <x:c r="T1" s="29"/>
+      <x:c r="U1" s="29"/>
+      <x:c r="V1" s="29"/>
+      <x:c r="W1" s="29"/>
+      <x:c r="X1" s="29"/>
+      <x:c r="Y1" s="29"/>
+    </x:row>
+    <x:row r="2" ht="60" customHeight="1">
+      <x:c r="A2" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B2" s="25" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C2" s="25" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D2" s="25" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E2" s="25" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F2" s="25">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G2" s="25" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H2" s="25">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I2" s="25" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J2" s="25">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K2" s="25" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L2" s="25" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="M2" s="25" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="N2" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="O2" s="25" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="P2" s="26"/>
+      <x:c r="Q2" s="27"/>
+      <x:c r="R2" s="27"/>
+      <x:c r="S2" s="27"/>
+      <x:c r="T2" s="27"/>
+      <x:c r="U2" s="27"/>
+      <x:c r="V2" s="27"/>
+      <x:c r="W2" s="27"/>
+      <x:c r="X2" s="27"/>
+      <x:c r="Y2" s="27"/>
+    </x:row>
+    <x:row r="3" ht="48" customHeight="1">
+      <x:c r="A3" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B3" s="25" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C3" s="25" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D3" s="25" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E3" s="25" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F3" s="25">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G3" s="25" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H3" s="25">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I3" s="25" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J3" s="25">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K3" s="25" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L3" s="25" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="M3" s="25" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="N3" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="O3" s="25" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="P3" s="26"/>
+      <x:c r="Q3" s="27"/>
+      <x:c r="R3" s="27"/>
+      <x:c r="S3" s="27"/>
+      <x:c r="T3" s="27"/>
+      <x:c r="U3" s="27"/>
+      <x:c r="V3" s="27"/>
+      <x:c r="W3" s="27"/>
+      <x:c r="X3" s="27"/>
+      <x:c r="Y3" s="27"/>
+    </x:row>
+    <x:row r="4" ht="60" customHeight="1">
+      <x:c r="A4" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B4" s="25" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C4" s="25" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D4" s="25" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E4" s="25" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F4" s="25">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G4" s="25" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H4" s="25">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I4" s="25" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J4" s="25">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K4" s="25" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="L4" s="25" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="M4" s="25" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="N4" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="O4" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="P4" s="26"/>
+      <x:c r="Q4" s="27"/>
+      <x:c r="R4" s="27"/>
+      <x:c r="S4" s="27"/>
+      <x:c r="T4" s="27"/>
+      <x:c r="U4" s="27"/>
+      <x:c r="V4" s="27"/>
+      <x:c r="W4" s="27"/>
+      <x:c r="X4" s="27"/>
+      <x:c r="Y4" s="27"/>
+    </x:row>
+    <x:row r="5" ht="48" customHeight="1">
+      <x:c r="A5" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B5" s="25" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C5" s="25" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D5" s="25" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E5" s="25" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F5" s="25">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G5" s="25" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H5" s="25">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I5" s="25" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J5" s="25">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K5" s="25" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="L5" s="25" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="M5" s="25" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="N5" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="O5" s="25" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="P5" s="26"/>
+      <x:c r="Q5" s="27"/>
+      <x:c r="R5" s="27"/>
+      <x:c r="S5" s="27"/>
+      <x:c r="T5" s="27"/>
+      <x:c r="U5" s="27"/>
+      <x:c r="V5" s="27"/>
+      <x:c r="W5" s="27"/>
+      <x:c r="X5" s="27"/>
+      <x:c r="Y5" s="27"/>
+    </x:row>
+    <x:row r="6" ht="60" customHeight="1">
+      <x:c r="A6" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B6" s="25" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C6" s="25" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D6" s="25" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E6" s="25" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F6" s="25">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G6" s="25" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H6" s="25">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I6" s="25" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J6" s="25">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K6" s="25" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L6" s="25" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M6" s="25" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="N6" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="O6" s="25" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="P6" s="26"/>
+      <x:c r="Q6" s="27"/>
+      <x:c r="R6" s="27"/>
+      <x:c r="S6" s="27"/>
+      <x:c r="T6" s="27"/>
+      <x:c r="U6" s="27"/>
+      <x:c r="V6" s="27"/>
+      <x:c r="W6" s="27"/>
+      <x:c r="X6" s="27"/>
+      <x:c r="Y6" s="27"/>
+    </x:row>
+    <x:row r="7" ht="39.599998474121094" customHeight="1">
+      <x:c r="A7" s="21" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B7" s="27" t="str">
+        <x:v>teo-yeopo-clemys</x:v>
+      </x:c>
+      <x:c r="C7" s="25" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D7" s="27"/>
+      <x:c r="E7" s="25" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F7" s="25">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G7" s="25" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H7" s="25">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I7" s="25" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J7" s="25">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K7" s="25" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L7" s="25" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="M7" s="25" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="N7" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="O7" s="25" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="P7" s="27"/>
+      <x:c r="Q7" s="27"/>
+      <x:c r="R7" s="27"/>
+      <x:c r="S7" s="27"/>
+      <x:c r="T7" s="27"/>
+      <x:c r="U7" s="27"/>
+      <x:c r="V7" s="27"/>
+      <x:c r="W7" s="27"/>
+      <x:c r="X7" s="27"/>
+      <x:c r="Y7" s="27"/>
+    </x:row>
+    <x:row r="8" ht="26.450000762939453" customHeight="1">
+      <x:c r="A8" s="21" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B8" s="27" t="str">
+        <x:v>ludgride-son-ogong-chancellor</x:v>
+      </x:c>
+      <x:c r="C8" s="25" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D8" s="27"/>
+      <x:c r="E8" s="25" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F8" s="25">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="25" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H8" s="25">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I8" s="25" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J8" s="25">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K8" s="25" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="L8" s="25" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="M8" s="25" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="N8" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="O8" s="25" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="P8" s="27"/>
+      <x:c r="Q8" s="27"/>
+      <x:c r="R8" s="27"/>
+      <x:c r="S8" s="27"/>
+      <x:c r="T8" s="27"/>
+      <x:c r="U8" s="27"/>
+      <x:c r="V8" s="27"/>
+      <x:c r="W8" s="27"/>
+      <x:c r="X8" s="27"/>
+      <x:c r="Y8" s="27"/>
+    </x:row>
+    <x:row r="9" ht="40.5">
+      <x:c r="A9" s="21" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B9" s="27" t="str">
+        <x:v>branz-bransel-yeopo-kyle</x:v>
+      </x:c>
+      <x:c r="C9" s="27" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D9" s="27"/>
+      <x:c r="E9" s="27" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F9" s="27">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G9" s="27" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H9" s="27">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I9" s="27" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J9" s="27">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K9" s="27" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L9" s="27" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="M9" s="25" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="N9" s="27"/>
+      <x:c r="O9" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="P9" s="27"/>
+      <x:c r="Q9" s="27"/>
+      <x:c r="R9" s="27"/>
+      <x:c r="S9" s="27"/>
+      <x:c r="T9" s="27"/>
+      <x:c r="U9" s="27"/>
+      <x:c r="V9" s="27"/>
+      <x:c r="W9" s="27"/>
+      <x:c r="X9" s="27"/>
+      <x:c r="Y9" s="27"/>
+    </x:row>
+    <x:row r="10" ht="16.5">
+      <x:c r="A10" s="21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B10" s="27" t="str">
+        <x:v>ludgride-son-ogong-chancellor-2</x:v>
+      </x:c>
+      <x:c r="C10" s="25" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D10" s="27"/>
+      <x:c r="E10" s="25" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F10" s="25">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="25" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H10" s="25">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I10" s="25" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J10" s="25">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K10" s="25" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="L10" s="27" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="M10" s="27" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="N10" s="27"/>
+      <x:c r="O10" s="27" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="P10" s="27"/>
+      <x:c r="Q10" s="27"/>
+      <x:c r="R10" s="27"/>
+      <x:c r="S10" s="27"/>
+      <x:c r="T10" s="27"/>
+      <x:c r="U10" s="27"/>
+      <x:c r="V10" s="27"/>
+      <x:c r="W10" s="27"/>
+      <x:c r="X10" s="27"/>
+      <x:c r="Y10" s="27"/>
+    </x:row>
+    <x:row r="11" ht="16.5">
+      <x:c r="A11" s="21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B11" s="27" t="str">
+        <x:v>ludgride-son-ogong-chancellor-3</x:v>
+      </x:c>
+      <x:c r="C11" s="25" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D11" s="27"/>
+      <x:c r="E11" s="25" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F11" s="25">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="25" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H11" s="25">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I11" s="25" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J11" s="25">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K11" s="25" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="L11" s="27" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="M11" s="27" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="N11" s="27"/>
+      <x:c r="O11" s="27" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="P11" s="27"/>
+      <x:c r="Q11" s="27"/>
+      <x:c r="R11" s="27"/>
+      <x:c r="S11" s="27"/>
+      <x:c r="T11" s="27"/>
+      <x:c r="U11" s="27"/>
+      <x:c r="V11" s="27"/>
+      <x:c r="W11" s="27"/>
+      <x:c r="X11" s="27"/>
+      <x:c r="Y11" s="27"/>
+    </x:row>
+    <x:row r="12" ht="27">
+      <x:c r="A12" s="21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B12" s="27" t="str">
+        <x:v>ludgride-tuto-chancellor</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D12" s="27"/>
+      <x:c r="E12" s="27" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F12" s="27">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H12" s="27">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I12" s="27" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="J12" s="27">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K12" s="27" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="L12" s="27" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="M12" s="25" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="N12" s="27"/>
+      <x:c r="O12" s="27" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="P12" s="27"/>
+      <x:c r="Q12" s="27"/>
+      <x:c r="R12" s="27"/>
+      <x:c r="S12" s="27"/>
+      <x:c r="T12" s="27"/>
+      <x:c r="U12" s="27"/>
+      <x:c r="V12" s="27"/>
+      <x:c r="W12" s="27"/>
+      <x:c r="X12" s="27"/>
+      <x:c r="Y12" s="27"/>
+    </x:row>
+    <x:row r="13" ht="27">
+      <x:c r="A13" s="21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B13" s="27" t="str">
+        <x:v>ludgride-son-ogong-tuto</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D13" s="27"/>
+      <x:c r="E13" s="27" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F13" s="27">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H13" s="27">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I13" s="27" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J13" s="27">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K13" s="27" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="L13" s="27" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="M13" s="25" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="N13" s="27"/>
+      <x:c r="O13" s="27" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="P13" s="27"/>
+      <x:c r="Q13" s="27"/>
+      <x:c r="R13" s="27"/>
+      <x:c r="S13" s="27"/>
+      <x:c r="T13" s="27"/>
+      <x:c r="U13" s="27"/>
+      <x:c r="V13" s="27"/>
+      <x:c r="W13" s="27"/>
+      <x:c r="X13" s="27"/>
+      <x:c r="Y13" s="27"/>
+    </x:row>
+    <x:row r="14" ht="40.5">
+      <x:c r="A14" s="21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B14" s="27" t="str">
+        <x:v>branz-bransel-yeopo-teo</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D14" s="27"/>
+      <x:c r="E14" s="27" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F14" s="27">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G14" s="27" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H14" s="27">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I14" s="27" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J14" s="27">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K14" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L14" s="27" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="M14" s="25" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="N14" s="27"/>
+      <x:c r="O14" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="P14" s="27"/>
+      <x:c r="Q14" s="27"/>
+      <x:c r="R14" s="27"/>
+      <x:c r="S14" s="27"/>
+      <x:c r="T14" s="27"/>
+      <x:c r="U14" s="27"/>
+      <x:c r="V14" s="27"/>
+      <x:c r="W14" s="27"/>
+      <x:c r="X14" s="27"/>
+      <x:c r="Y14" s="27"/>
+    </x:row>
+    <x:row r="15" ht="40.5">
+      <x:c r="A15" s="21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B15" s="27" t="str">
+        <x:v>branz-bransel-yeopo-teo-2</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D15" s="27"/>
+      <x:c r="E15" s="27" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F15" s="27">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G15" s="27" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H15" s="27">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I15" s="27" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J15" s="27">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K15" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L15" s="27" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="M15" s="25" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="N15" s="27"/>
+      <x:c r="O15" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="P15" s="27"/>
+      <x:c r="Q15" s="27"/>
+      <x:c r="R15" s="27"/>
+      <x:c r="S15" s="27"/>
+      <x:c r="T15" s="27"/>
+      <x:c r="U15" s="27"/>
+      <x:c r="V15" s="27"/>
+      <x:c r="W15" s="27"/>
+      <x:c r="X15" s="27"/>
+      <x:c r="Y15" s="27"/>
+    </x:row>
+    <x:row r="16" ht="40.5">
+      <x:c r="A16" s="21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B16" s="27" t="str">
+        <x:v>branz-bransel-yeopo-teo-3</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D16" s="27"/>
+      <x:c r="E16" s="27" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F16" s="27">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G16" s="27" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H16" s="27">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I16" s="27" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J16" s="27">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K16" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L16" s="27" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="M16" s="25" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="N16" s="27"/>
+      <x:c r="O16" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="P16" s="27"/>
+      <x:c r="Q16" s="27"/>
+      <x:c r="R16" s="27"/>
+      <x:c r="S16" s="27"/>
+      <x:c r="T16" s="27"/>
+      <x:c r="U16" s="27"/>
+      <x:c r="V16" s="27"/>
+      <x:c r="W16" s="27"/>
+      <x:c r="X16" s="27"/>
+      <x:c r="Y16" s="27"/>
+    </x:row>
+    <x:row r="17" ht="40.5">
+      <x:c r="A17" s="21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B17" s="27" t="str">
+        <x:v>landgride-teo-kyle</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D17" s="27"/>
+      <x:c r="E17" s="27" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F17" s="27">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G17" s="27" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H17" s="27">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I17" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J17" s="27">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K17" s="27" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L17" s="27" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="M17" s="25" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="N17" s="27"/>
+      <x:c r="O17" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="P17" s="27"/>
+      <x:c r="Q17" s="27"/>
+      <x:c r="R17" s="27"/>
+      <x:c r="S17" s="27"/>
+      <x:c r="T17" s="27"/>
+      <x:c r="U17" s="27"/>
+      <x:c r="V17" s="27"/>
+      <x:c r="W17" s="27"/>
+      <x:c r="X17" s="27"/>
+      <x:c r="Y17" s="27"/>
+    </x:row>
+    <x:row r="18" ht="40.5">
+      <x:c r="A18" s="21" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B18" s="27" t="str">
+        <x:v>landgride-yeopo-branz-bransel</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D18" s="27"/>
+      <x:c r="E18" s="27" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F18" s="27">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="27" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H18" s="27">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I18" s="27" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J18" s="27">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K18" s="27" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L18" s="27" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="M18" s="25" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="N18" s="27"/>
+      <x:c r="O18" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="P18" s="27"/>
+      <x:c r="Q18" s="27"/>
+      <x:c r="R18" s="27"/>
+      <x:c r="S18" s="27"/>
+      <x:c r="T18" s="27"/>
+      <x:c r="U18" s="27"/>
+      <x:c r="V18" s="27"/>
+      <x:c r="W18" s="27"/>
+      <x:c r="X18" s="27"/>
+      <x:c r="Y18" s="27"/>
+    </x:row>
+    <x:row r="19" ht="40.5">
+      <x:c r="A19" s="21" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B19" s="27" t="str">
+        <x:v>landgride-yeopo-branz-bransel-2</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D19" s="27"/>
+      <x:c r="E19" s="27" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F19" s="27">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G19" s="27" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H19" s="27">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I19" s="27" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J19" s="27">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K19" s="27" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L19" s="27" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="M19" s="25" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="N19" s="27"/>
+      <x:c r="O19" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="P19" s="27"/>
+      <x:c r="Q19" s="27"/>
+      <x:c r="R19" s="27"/>
+      <x:c r="S19" s="27"/>
+      <x:c r="T19" s="27"/>
+      <x:c r="U19" s="27"/>
+      <x:c r="V19" s="27"/>
+      <x:c r="W19" s="27"/>
+      <x:c r="X19" s="27"/>
+      <x:c r="Y19" s="27"/>
+    </x:row>
+    <x:row r="20" ht="40.5">
+      <x:c r="A20" s="21" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B20" s="27" t="str">
+        <x:v>branz-bransel-yeopo-kyle-2</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D20" s="27"/>
+      <x:c r="E20" s="27" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F20" s="27">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G20" s="27" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H20" s="27">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I20" s="27" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J20" s="27">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K20" s="27" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L20" s="27" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="M20" s="25" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="N20" s="27"/>
+      <x:c r="O20" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="P20" s="27"/>
+      <x:c r="Q20" s="27"/>
+      <x:c r="R20" s="27"/>
+      <x:c r="S20" s="27"/>
+      <x:c r="T20" s="27"/>
+      <x:c r="U20" s="27"/>
+      <x:c r="V20" s="27"/>
+      <x:c r="W20" s="27"/>
+      <x:c r="X20" s="27"/>
+      <x:c r="Y20" s="27"/>
+    </x:row>
+    <x:row r="21" ht="42.75">
+      <x:c r="A21" s="21" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>landgride-teo-yeopo</x:v>
+      </x:c>
+      <x:c r="C21" s="32" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="E21" s="32" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F21" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G21" s="32" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H21" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I21" s="32" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J21" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K21" s="32" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="L21" s="32" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="M21" s="33" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="O21" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="49.5">
+      <x:c r="A22" s="21" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>landgride-teo-kyle-2</x:v>
+      </x:c>
+      <x:c r="C22" s="32" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="E22" s="32" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F22" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G22" s="32" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H22" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I22" s="32" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J22" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K22" s="32" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L22" s="32" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="M22" s="34" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="O22" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="16.5">
+      <x:c r="A23" s="21" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>ludgride-son-ogong-gelidus</x:v>
+      </x:c>
+      <x:c r="C23" s="32" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="E23" s="32" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F23" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" s="32" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H23" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I23" s="32" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J23" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K23" s="32" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="L23" s="32" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="M23" s="35" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="O23" s="32" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42.75">
+      <x:c r="A24" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>milia-freya-reginleif</x:v>
+      </x:c>
+      <x:c r="C24" s="32" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="E24" s="32" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F24" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" s="32" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H24" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I24" s="32" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J24" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K24" s="32" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="L24" s="32" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="M24" s="33" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="O24" s="32" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="49.5">
+      <x:c r="A25" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>pi-landgride-kyle</x:v>
+      </x:c>
+      <x:c r="C25" s="32" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="E25" s="32" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F25" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G25" s="32" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H25" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I25" s="32" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J25" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K25" s="32" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L25" s="32" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="M25" s="34" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="O25" s="32" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="49.5">
+      <x:c r="A26" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>pi-landgride-kyle-2</x:v>
+      </x:c>
+      <x:c r="C26" s="32" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="E26" s="32" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F26" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G26" s="32" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H26" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I26" s="32" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J26" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K26" s="32" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L26" s="32" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="M26" s="34" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="O26" s="32" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="42.75">
+      <x:c r="A27" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>melkir-run-reginleif</x:v>
+      </x:c>
+      <x:c r="C27" s="32" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="E27" s="32" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G27" s="32" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H27" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I27" s="32" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J27" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K27" s="32" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="L27" s="32" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="M27" s="33" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="O27" s="32" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="42.75">
+      <x:c r="A28" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>omok-freya-run</x:v>
+      </x:c>
+      <x:c r="C28" s="32" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="E28" s="32" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F28" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G28" s="32" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H28" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I28" s="32" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J28" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K28" s="32" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L28" s="32" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="M28" s="33" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="O28" s="32" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="42.75">
+      <x:c r="A29" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>milia-omok-run</x:v>
+      </x:c>
+      <x:c r="C29" s="32" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="E29" s="32" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F29" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" s="32" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H29" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I29" s="32" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J29" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K29" s="32" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L29" s="32" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="M29" s="33" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="O29" s="32" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="42.75">
+      <x:c r="A30" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>milia-omok-run-2</x:v>
+      </x:c>
+      <x:c r="C30" s="32" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="E30" s="32" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F30" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G30" s="32" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H30" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I30" s="32" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J30" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K30" s="32" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L30" s="32" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="M30" s="33" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="O30" s="32" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="30">
+      <x:c r="A31" s="21" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>landgride-yeopo-counter</x:v>
+      </x:c>
+      <x:c r="C31" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="E31" s="32" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F31" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G31" s="32" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H31" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I31" s="32" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J31" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K31" s="32" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="L31" s="32" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="M31" s="33" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="O31" s="32" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="16.5">
+      <x:c r="A32" s="21" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>ludgride-son-ogong-counter</x:v>
+      </x:c>
+      <x:c r="C32" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="E32" s="32" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F32" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G32" s="32" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H32" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I32" s="32" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J32" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K32" s="32" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="L32" s="32" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="M32" s="33" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="O32" s="32" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="42.75">
+      <x:c r="A33" s="21" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>landgride-kyle-blista</x:v>
+      </x:c>
+      <x:c r="C33" s="32" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="E33" s="32" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F33" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G33" s="32" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H33" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I33" s="32" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J33" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K33" s="32" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="L33" s="32" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="M33" s="33" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="O33" s="32" t="s">
+        <x:v>201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="16.5">
+      <x:c r="A34" s="21" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>platin-aragon-counter</x:v>
+      </x:c>
+      <x:c r="C34" s="32" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="E34" s="32" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F34" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G34" s="32" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H34" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I34" s="32" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="J34" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K34" s="32" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="L34" s="32" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="M34" s="33" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="O34" s="32" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="42.75">
+      <x:c r="A35" s="21" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>milia-freya-reginleif-2</x:v>
+      </x:c>
+      <x:c r="C35" s="32" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="E35" s="32" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F35" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G35" s="32" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H35" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I35" s="32" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J35" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K35" s="32" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="L35" s="32" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="M35" s="33" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="O35" s="32" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="42.75">
+      <x:c r="A36" s="21" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>milia-freya-reginleif-3</x:v>
+      </x:c>
+      <x:c r="C36" s="32" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="E36" s="32" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F36" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G36" s="32" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H36" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I36" s="32" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J36" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K36" s="32" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="L36" s="32" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="M36" s="33" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="O36" s="32" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="42.75">
+      <x:c r="A37" s="21" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>vanessa-freya-reginleif</x:v>
+      </x:c>
+      <x:c r="C37" s="32" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="E37" s="32" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F37" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G37" s="32" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="H37" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I37" s="32" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J37" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K37" s="32" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="L37" s="32" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="M37" s="33" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="O37" s="32" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="42.75">
+      <x:c r="A38" s="21" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>rosie-aquila-mist</x:v>
+      </x:c>
+      <x:c r="C38" s="32" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="E38" s="32" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F38" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G38" s="32" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H38" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I38" s="32" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="J38" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K38" s="32" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="L38" s="32" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="M38" s="33" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="O38" s="32" t="s">
+        <x:v>218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="42.75">
+      <x:c r="A39" s="21" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>rosie-nox-mist</x:v>
+      </x:c>
+      <x:c r="C39" s="32" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="E39" s="32" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F39" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G39" s="32" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H39" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I39" s="32" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="J39" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K39" s="32" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="L39" s="32" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="M39" s="33" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="O39" s="32" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="16.5">
+      <x:c r="A40" s="21" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>ludgride-son-ogong-ace</x:v>
+      </x:c>
+      <x:c r="C40" s="32" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="E40" s="32" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F40" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G40" s="32" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H40" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I40" s="32" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J40" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K40" s="32" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="L40" s="32" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="M40" s="33" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="O40" s="32" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="42.75">
+      <x:c r="A41" s="21" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D1" s="10" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E1" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F1" s="10" t="s">
+      <x:c r="B41" t="str">
+        <x:v>landgride-karl-heron-yeopo</x:v>
+      </x:c>
+      <x:c r="C41" s="32" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="E41" s="32" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F41" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G41" s="32" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H41" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I41" s="32" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="J41" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K41" s="32" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="L41" s="32" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="M41" s="33" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="O41" s="32" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="16.5">
+      <x:c r="A42" s="21" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G1" s="10" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H1" s="10" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="I1" s="10" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="J1" s="10" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="K1" s="10" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="L1" s="10" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="M1" s="10" t="s">
+      <x:c r="B42" t="str">
+        <x:v>ludgride-son-ogong-chancellor-4</x:v>
+      </x:c>
+      <x:c r="C42" s="32" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E42" s="32" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F42" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G42" s="32" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H42" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I42" s="32" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J42" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K42" s="32" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="L42" s="32" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="M42" s="33" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="O42" s="32" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="42.75">
+      <x:c r="A43" s="21" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>teo-karl-heron-branz-bransel</x:v>
+      </x:c>
+      <x:c r="C43" s="32" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="E43" s="32" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F43" s="32">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G43" s="32" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H43" s="32">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I43" s="32" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="J43" s="32">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K43" s="32" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L43" s="32" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="M43" s="33" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="O43" s="32" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="28.5">
+      <x:c r="A44" s="21" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="N1" s="10" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="O1" s="10" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="P1" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="71.25">
-      <x:c r="A2" s="12" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B2" s="13" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C2" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D2" s="13" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E2" s="13" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F2" s="13">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G2" s="13" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H2" s="13">
+      <x:c r="B44" t="str">
+        <x:v>platin-rudy-alice</x:v>
+      </x:c>
+      <x:c r="C44" s="32" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="E44" s="32" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F44" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G44" s="32" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H44" s="32">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I2" s="13" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="J2" s="13">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K2" s="13" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L2" s="13" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="M2" s="13" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="N2" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="O2" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="P2" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="57">
-      <x:c r="A3" s="12" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B3" s="13" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C3" s="13" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D3" s="13" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F3" s="13">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H3" s="13">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I3" s="13" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="J3" s="13">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K3" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L3" s="13" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="M3" s="13" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="N3" s="13" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="O3" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="P3" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="71.25">
-      <x:c r="A4" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B4" s="13" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C4" s="13" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D4" s="13" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E4" s="13" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F4" s="13">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G4" s="13" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H4" s="13">
+      <x:c r="I44" s="32" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="J44" s="32">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I4" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="J4" s="13">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K4" s="13" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="L4" s="13" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="M4" s="13" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="N4" s="13" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="O4" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="P4" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="57">
-      <x:c r="A5" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B5" s="13" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C5" s="13" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D5" s="13" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="E5" s="13" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F5" s="13">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G5" s="13" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="H5" s="13">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I5" s="13" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="J5" s="13">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K5" s="13" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="L5" s="13" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="M5" s="13" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="N5" s="13" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="O5" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="P5" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="71.25">
-      <x:c r="A6" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B6" s="16" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C6" s="16" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D6" s="16" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E6" s="16" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F6" s="16">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G6" s="16" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H6" s="16">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I6" s="16" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="J6" s="16">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K6" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L6" s="16" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="M6" s="16" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="N6" s="16" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="O6" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="P6" s="17" t="s">
-        <x:v>121</x:v>
-      </x:c>
+      <x:c r="K44" s="32" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L44" s="32" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="M44" s="33" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="O44" s="32" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="C45" s="32"/>
+      <x:c r="E45" s="32"/>
+      <x:c r="F45" s="32"/>
+      <x:c r="G45" s="32"/>
+      <x:c r="H45" s="32"/>
+      <x:c r="I45" s="32"/>
+      <x:c r="J45" s="32"/>
+      <x:c r="K45" s="32"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2435,1190 +4940,1190 @@
   <x:sheetData>
     <x:row r="1" ht="15">
       <x:c r="A1" s="9" t="s">
-        <x:v>122</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B1" s="10" t="s">
-        <x:v>123</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C1" s="11" t="s">
-        <x:v>124</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="s">
-        <x:v>125</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B2" s="13" t="s">
-        <x:v>87</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C2" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B3" s="13" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C3" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="s">
-        <x:v>129</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B4" s="13" t="s">
-        <x:v>88</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C4" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="s">
-        <x:v>131</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B5" s="13" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="C5" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="s">
-        <x:v>132</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B6" s="13" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C6" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B7" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="s">
-        <x:v>135</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="12" t="s">
-        <x:v>137</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="12" t="s">
-        <x:v>139</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="12" t="s">
-        <x:v>140</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B13" s="13" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="12" t="s">
-        <x:v>144</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>145</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="12" t="s">
-        <x:v>146</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B16" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="12" t="s">
-        <x:v>148</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>149</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="12" t="s">
-        <x:v>150</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B18" s="13" t="s">
-        <x:v>151</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="12" t="s">
-        <x:v>152</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>153</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B20" s="13" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>156</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="12" t="s">
-        <x:v>157</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
-        <x:v>158</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="12" t="s">
-        <x:v>159</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B23" s="13" t="s">
-        <x:v>160</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="12" t="s">
-        <x:v>161</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B24" s="13" t="s">
-        <x:v>162</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="12" t="s">
-        <x:v>163</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B25" s="13" t="s">
-        <x:v>164</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="12" t="s">
-        <x:v>165</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B26" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="12" t="s">
-        <x:v>166</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>167</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="12" t="s">
-        <x:v>168</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B28" s="13" t="s">
-        <x:v>169</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="12" t="s">
-        <x:v>170</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>171</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C29" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="12" t="s">
-        <x:v>172</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B30" s="13" t="s">
-        <x:v>173</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C30" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="12" t="s">
-        <x:v>174</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>175</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C31" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="12" t="s">
-        <x:v>176</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B32" s="13" t="s">
-        <x:v>111</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C32" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="12" t="s">
-        <x:v>177</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>178</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C33" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="12" t="s">
-        <x:v>179</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B34" s="13" t="s">
-        <x:v>180</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C34" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="12" t="s">
-        <x:v>181</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>182</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C35" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="12" t="s">
-        <x:v>183</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
-        <x:v>184</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C36" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="12" t="s">
-        <x:v>185</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
-        <x:v>186</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C37" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="12" t="s">
-        <x:v>187</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
-        <x:v>188</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C38" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="12" t="s">
-        <x:v>189</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B39" s="13" t="s">
-        <x:v>190</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C39" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="12" t="s">
-        <x:v>191</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>192</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C40" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="12" t="s">
-        <x:v>193</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
-        <x:v>194</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C41" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="12" t="s">
-        <x:v>195</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>196</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C42" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="12" t="s">
-        <x:v>197</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>198</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C43" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="12" t="s">
-        <x:v>199</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B44" s="13" t="s">
-        <x:v>200</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C44" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="12" t="s">
-        <x:v>201</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B45" s="13" t="s">
-        <x:v>202</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C45" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="12" t="s">
-        <x:v>203</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B46" s="13" t="s">
-        <x:v>204</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C46" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="12" t="s">
-        <x:v>205</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B47" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C47" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="12" t="s">
-        <x:v>207</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B48" s="13" t="s">
-        <x:v>208</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C48" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="12" t="s">
-        <x:v>209</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B49" s="13" t="s">
-        <x:v>210</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C49" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="12" t="s">
-        <x:v>211</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B50" s="13" t="s">
-        <x:v>212</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C50" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="12" t="s">
-        <x:v>213</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B51" s="13" t="s">
-        <x:v>214</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C51" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="12" t="s">
-        <x:v>215</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B52" s="13" t="s">
-        <x:v>216</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C52" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="12" t="s">
-        <x:v>217</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B53" s="13" t="s">
-        <x:v>218</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C53" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="12" t="s">
-        <x:v>219</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B54" s="13" t="s">
-        <x:v>220</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C54" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="12" t="s">
-        <x:v>221</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B55" s="13" t="s">
-        <x:v>222</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C55" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="12" t="s">
-        <x:v>223</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B56" s="13" t="s">
-        <x:v>224</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C56" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="12" t="s">
-        <x:v>225</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B57" s="13" t="s">
-        <x:v>226</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C57" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="12" t="s">
-        <x:v>227</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B58" s="13" t="s">
-        <x:v>228</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C58" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="12" t="s">
-        <x:v>229</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B59" s="13" t="s">
-        <x:v>230</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C59" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="12" t="s">
-        <x:v>231</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B60" s="13" t="s">
-        <x:v>232</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C60" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="12" t="s">
-        <x:v>233</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B61" s="13" t="s">
-        <x:v>234</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C61" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="12" t="s">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B62" s="13" t="s">
-        <x:v>236</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C62" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="12" t="s">
-        <x:v>237</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B63" s="13" t="s">
-        <x:v>238</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C63" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="12" t="s">
-        <x:v>239</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B64" s="13" t="s">
-        <x:v>240</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C64" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="12" t="s">
-        <x:v>241</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B65" s="13" t="s">
-        <x:v>242</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C65" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="12" t="s">
-        <x:v>243</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B66" s="13" t="s">
-        <x:v>244</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C66" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="12" t="s">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B67" s="13" t="s">
-        <x:v>246</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C67" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="12" t="s">
-        <x:v>247</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B68" s="13" t="s">
-        <x:v>248</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="C68" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="12" t="s">
-        <x:v>249</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B69" s="13" t="s">
-        <x:v>250</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C69" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="12" t="s">
-        <x:v>251</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B70" s="13" t="s">
-        <x:v>252</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C70" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="12" t="s">
-        <x:v>253</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B71" s="13" t="s">
-        <x:v>254</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C71" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="12" t="s">
-        <x:v>255</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B72" s="13" t="s">
-        <x:v>256</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C72" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="12" t="s">
-        <x:v>257</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B73" s="13" t="s">
-        <x:v>258</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="C73" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="12" t="s">
-        <x:v>259</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B74" s="13" t="s">
-        <x:v>260</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C74" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="12" t="s">
-        <x:v>261</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B75" s="13" t="s">
-        <x:v>262</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="C75" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="12" t="s">
-        <x:v>263</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B76" s="13" t="s">
-        <x:v>264</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C76" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="12" t="s">
-        <x:v>265</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B77" s="13" t="s">
-        <x:v>266</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="C77" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="12" t="s">
-        <x:v>267</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B78" s="13" t="s">
-        <x:v>268</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C78" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="12" t="s">
-        <x:v>269</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B79" s="13" t="s">
-        <x:v>270</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="C79" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="12" t="s">
-        <x:v>271</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B80" s="13" t="s">
-        <x:v>272</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="C80" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="12" t="s">
-        <x:v>273</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B81" s="13" t="s">
-        <x:v>274</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C81" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="12" t="s">
-        <x:v>275</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B82" s="13" t="s">
-        <x:v>276</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="C82" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B83" s="13" t="s">
-        <x:v>278</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="C83" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="12" t="s">
-        <x:v>279</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B84" s="13" t="s">
-        <x:v>280</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="C84" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="12" t="s">
-        <x:v>281</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B85" s="13" t="s">
-        <x:v>282</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C85" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="12" t="s">
-        <x:v>283</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B86" s="13" t="s">
-        <x:v>284</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C86" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="12" t="s">
-        <x:v>285</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B87" s="13" t="s">
-        <x:v>286</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="C87" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="12" t="s">
-        <x:v>287</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B88" s="13" t="s">
-        <x:v>288</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="C88" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="12" t="s">
-        <x:v>289</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B89" s="13" t="s">
-        <x:v>290</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C89" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="12" t="s">
-        <x:v>291</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B90" s="13" t="s">
-        <x:v>292</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="C90" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="12" t="s">
-        <x:v>293</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B91" s="13" t="s">
-        <x:v>294</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="C91" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="12" t="s">
-        <x:v>295</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B92" s="13" t="s">
-        <x:v>296</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="C92" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="12" t="s">
-        <x:v>297</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B93" s="13" t="s">
-        <x:v>298</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="C93" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="12" t="s">
-        <x:v>299</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B94" s="13" t="s">
-        <x:v>300</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="C94" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="12" t="s">
-        <x:v>301</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B95" s="13" t="s">
-        <x:v>302</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="C95" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B96" s="13" t="s">
-        <x:v>304</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C96" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="12" t="s">
-        <x:v>305</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B97" s="13" t="s">
-        <x:v>306</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="C97" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="12" t="s">
-        <x:v>307</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B98" s="13" t="s">
-        <x:v>308</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="C98" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="12" t="s">
-        <x:v>309</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B99" s="13" t="s">
-        <x:v>310</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="C99" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="12" t="s">
-        <x:v>311</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B100" s="13" t="s">
-        <x:v>312</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C100" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="12" t="s">
-        <x:v>313</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B101" s="13" t="s">
-        <x:v>314</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="C101" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="12" t="s">
-        <x:v>315</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B102" s="13" t="s">
-        <x:v>316</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="C102" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="12" t="s">
-        <x:v>317</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B103" s="13" t="s">
-        <x:v>318</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C103" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="12" t="s">
-        <x:v>319</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B104" s="13" t="s">
-        <x:v>320</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="C104" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="12" t="s">
-        <x:v>321</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B105" s="13" t="s">
-        <x:v>322</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="C105" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="12" t="s">
-        <x:v>323</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B106" s="13" t="s">
-        <x:v>324</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="C106" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="12" t="s">
-        <x:v>325</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B107" s="13" t="s">
-        <x:v>326</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="C107" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="15" t="s">
-        <x:v>327</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B108" s="16" t="s">
-        <x:v>328</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="C108" s="17" t="s">
-        <x:v>130</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/seven-knights-counter-app/counter-template.xlsx
+++ b/seven-knights-counter-app/counter-template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="1" r:id="R75e7e6a685b84d5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="방어팀" sheetId="2" r:id="Rfbf6a4f6d0e949bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공략덱" sheetId="3" r:id="R3eb2f27a0bef4e8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참조_영웅" sheetId="4" r:id="Rd13dae905930460a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참조_펫" sheetId="5" r:id="R2028bc8c70a54bf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="1" r:id="R56006d5b31f247cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="방어팀" sheetId="2" r:id="R2ec4aa3a285e43e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공략덱" sheetId="3" r:id="R8d22b5f900034804"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참조_영웅" sheetId="4" r:id="R793e3bc3249b4f12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참조_펫" sheetId="5" r:id="R67d79a76be774a3c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -455,6 +455,21 @@
     <x:t xml:space="preserve">로지</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">실밀스</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">실베스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">스쿨드</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오밀스</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">프밀스</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">공략덱ID</x:t>
   </x:si>
   <x:si>
@@ -945,6 +960,181 @@
     <x:t xml:space="preserve">효저세공 반지+ 셋다 효저 90이상 받받+ 막기 챙기기(조율자 필수)</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">라겔오</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오2 겔2 오1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">유</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여델칼</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">델론즈</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여1 여2 델2</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">여포</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Arial"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">: </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">불사</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Arial"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">, </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">권능
+델론즈</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Arial"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">: </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">불사
+칼</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Arial"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">: </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">권능</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Arial"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">, </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="맑은 고딕"/>
+        <x:family val="3"/>
+      </x:rPr>
+      <x:t xml:space="preserve">불사</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">밀멜스</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">스2 스1 스각</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">멜키르: 권능+기합</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">멜패로</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">델카란</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">델2 카2 카1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">란드: 불사
+델론즈: 불사
+카일: 권능, 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">속공따야함
+오목 1스를 카일2스 버프제거</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">델여쁘</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">여1 델2 여2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">브브: 불사
+여포: 불사, 권능
+델론즈: 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">제오</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">델파란</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">델1 델3 파2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">파이: 불사, 권능
+란드: 불사
+델론즈: 불사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">내실
+델론즈 효조,약공 100이상(스쿨드 쿨증 막기)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">밀린스</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">린2 스2 스1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">요랑</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">영웅ID</x:t>
   </x:si>
   <x:si>
@@ -984,9 +1174,6 @@
     <x:t xml:space="preserve">sylvester</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">실베스타</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">clemys</x:t>
   </x:si>
   <x:si>
@@ -1134,9 +1321,6 @@
     <x:t xml:space="preserve">delons</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">델론즈</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">kiriel</x:t>
   </x:si>
   <x:si>
@@ -1149,9 +1333,6 @@
     <x:t xml:space="preserve">skuld</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">스쿨드</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">aquila</x:t>
   </x:si>
   <x:si>
@@ -1504,13 +1685,187 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">아수라</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">펫ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">펫명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p01</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">전설</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p02</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">제브</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p03</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p04</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">카람</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p05</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p06</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">델로</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p07</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">리첼</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p08</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p09</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">파이크</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">루</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p11</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">연지</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">이린</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p13</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">크리</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p14</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">윈디</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">에리</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p16</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">더지</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p17</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">믹</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">크로아</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">희귀</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">파라곤</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">노트</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p21</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">세리</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p22</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">니키</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">니나</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p24</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">풍소협</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p25</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">뮤뮤</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p26</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">이그리트</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p27</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">미믹</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p28</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">두</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">p29</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">헬레핀</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="17">
+  <x:fonts count="21">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -1595,6 +1950,22 @@
       <x:sz val="11"/>
       <x:color rgb="FFFF0000"/>
       <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
   <x:fills count="11">
@@ -1821,7 +2192,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1907,10 +2278,31 @@
     <x:xf numFmtId="0" fontId="9" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="1"/>
@@ -2120,14 +2512,14 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="20.25">
-      <x:c r="A1" s="35" t="s">
+      <x:c r="A1" s="37" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="35"/>
-      <x:c r="C1" s="35"/>
-      <x:c r="D1" s="35"/>
-      <x:c r="E1" s="35"/>
-      <x:c r="F1" s="35"/>
+      <x:c r="B1" s="37"/>
+      <x:c r="C1" s="37"/>
+      <x:c r="D1" s="37"/>
+      <x:c r="E1" s="37"/>
+      <x:c r="F1" s="37"/>
     </x:row>
     <x:row r="3" ht="15">
       <x:c r="A3" s="1" t="s">
@@ -2501,9 +2893,66 @@
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="21" customHeight="1"/>
-    <x:row r="15" ht="21" customHeight="1"/>
-    <x:row r="16" ht="21" customHeight="1"/>
+    <x:row r="14" ht="21" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>sylvester-milia-skuld</x:v>
+      </x:c>
+      <x:c r="B14" s="38" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C14" s="38" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D14" s="38" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E14" s="38" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G14" s="19" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="21" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>omok-milia-skuld</x:v>
+      </x:c>
+      <x:c r="B15" s="38" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C15" s="38" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D15" s="38" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E15" s="38" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G15" s="19" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="21" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>freya-milia-skuld</x:v>
+      </x:c>
+      <x:c r="B16" s="38" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C16" s="38" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D16" s="38" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E16" s="38" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G16" s="19" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
     <x:row r="17" ht="21" customHeight="1">
       <x:c r="A17" s="18"/>
       <x:c r="B17" s="19"/>
@@ -2559,9 +3008,9 @@
     <x:col min="9" max="9" width="10" customWidth="1"/>
     <x:col min="10" max="10" width="16" customWidth="1"/>
     <x:col min="11" max="11" width="18" customWidth="1"/>
-    <x:col min="12" max="12" width="36" customWidth="1"/>
+    <x:col min="12" max="12" width="36" style="45" customWidth="1"/>
     <x:col min="13" max="14" width="12" customWidth="1"/>
-    <x:col min="15" max="15" width="18" customWidth="1"/>
+    <x:col min="15" max="15" width="23.125" style="45" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="21.950000762939453" customHeight="1">
@@ -2569,37 +3018,37 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B1" s="34" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C1" s="34" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D1" s="34" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E1" s="34" t="s">
-        <x:v>74</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F1" s="34" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G1" s="34" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H1" s="34" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I1" s="34" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J1" s="34" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K1" s="34" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="L1" s="34" t="s">
-        <x:v>81</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="M1" s="34" t="s">
         <x:v>19</x:v>
@@ -2626,19 +3075,19 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="24" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C2" s="25" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D2" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E2" s="25">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F2" s="25" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G2" s="25">
         <x:v>4</x:v>
@@ -2650,20 +3099,20 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J2" s="25" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K2" s="25" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="L2" s="25" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L2" s="43" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M2" s="25"/>
       <x:c r="N2" s="25" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="O2" s="25" t="s">
-        <x:v>89</x:v>
+      <x:c r="O2" s="43" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P2" s="26"/>
       <x:c r="Q2" s="24"/>
@@ -2681,13 +3130,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B3" s="24" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C3" s="25" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D3" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E3" s="25">
         <x:v>1</x:v>
@@ -2705,20 +3154,20 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J3" s="25" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K3" s="25" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="L3" s="25" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="L3" s="43" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M3" s="25"/>
       <x:c r="N3" s="25" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="O3" s="25" t="s">
-        <x:v>96</x:v>
+      <x:c r="O3" s="43" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P3" s="26"/>
       <x:c r="Q3" s="24"/>
@@ -2736,13 +3185,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="24" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C4" s="24" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D4" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E4" s="24">
         <x:v>2</x:v>
@@ -2760,18 +3209,18 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J4" s="24" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K4" s="25" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="L4" s="25" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="L4" s="43" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="M4" s="25"/>
       <x:c r="N4" s="25"/>
-      <x:c r="O4" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O4" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P4" s="26"/>
       <x:c r="Q4" s="24"/>
@@ -2789,13 +3238,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="24" t="s">
-        <x:v>102</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C5" s="25" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D5" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E5" s="25">
         <x:v>1</x:v>
@@ -2813,18 +3262,18 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J5" s="25" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K5" s="25" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="L5" s="25" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="L5" s="43" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M5" s="25"/>
       <x:c r="N5" s="25"/>
-      <x:c r="O5" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O5" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P5" s="26"/>
       <x:c r="Q5" s="24"/>
@@ -2842,13 +3291,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B6" s="24" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C6" s="25" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D6" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E6" s="25">
         <x:v>1</x:v>
@@ -2866,18 +3315,18 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J6" s="25" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K6" s="25" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="L6" s="25" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="L6" s="43" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M6" s="25"/>
       <x:c r="N6" s="25"/>
-      <x:c r="O6" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O6" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P6" s="26"/>
       <x:c r="Q6" s="24"/>
@@ -2895,13 +3344,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="24" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C7" s="24" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D7" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E7" s="24">
         <x:v>1</x:v>
@@ -2919,18 +3368,18 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J7" s="24" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K7" s="25" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="L7" s="25" t="s">
-        <x:v>108</x:v>
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="L7" s="43" t="s">
+        <x:v>113</x:v>
       </x:c>
       <x:c r="M7" s="25"/>
       <x:c r="N7" s="25"/>
-      <x:c r="O7" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O7" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P7" s="24"/>
       <x:c r="Q7" s="24"/>
@@ -2948,13 +3397,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="24" t="s">
-        <x:v>109</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C8" s="24" t="s">
-        <x:v>110</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D8" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E8" s="24">
         <x:v>1</x:v>
@@ -2975,15 +3424,15 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K8" s="25" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="L8" s="25" t="s">
-        <x:v>108</x:v>
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="L8" s="43" t="s">
+        <x:v>113</x:v>
       </x:c>
       <x:c r="M8" s="25"/>
       <x:c r="N8" s="25"/>
-      <x:c r="O8" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O8" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P8" s="24"/>
       <x:c r="Q8" s="24"/>
@@ -3001,13 +3450,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="24" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C9" s="24" t="s">
-        <x:v>113</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D9" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E9" s="24">
         <x:v>2</x:v>
@@ -3025,18 +3474,18 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J9" s="24" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K9" s="25" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="L9" s="25" t="s">
-        <x:v>88</x:v>
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="L9" s="43" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M9" s="25"/>
       <x:c r="N9" s="25"/>
-      <x:c r="O9" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O9" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P9" s="24"/>
       <x:c r="Q9" s="24"/>
@@ -3054,13 +3503,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="24" t="s">
-        <x:v>115</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C10" s="24" t="s">
-        <x:v>113</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D10" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E10" s="24">
         <x:v>2</x:v>
@@ -3078,18 +3527,18 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J10" s="24" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K10" s="25" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="L10" s="25" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L10" s="43" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M10" s="25"/>
       <x:c r="N10" s="25"/>
-      <x:c r="O10" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O10" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P10" s="24"/>
       <x:c r="Q10" s="24"/>
@@ -3107,13 +3556,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B11" s="24" t="s">
-        <x:v>116</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C11" s="24" t="s">
-        <x:v>113</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D11" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E11" s="24">
         <x:v>2</x:v>
@@ -3131,18 +3580,18 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J11" s="24" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K11" s="25" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="L11" s="25" t="s">
-        <x:v>88</x:v>
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="L11" s="43" t="s">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M11" s="25"/>
       <x:c r="N11" s="25"/>
-      <x:c r="O11" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O11" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P11" s="24"/>
       <x:c r="Q11" s="24"/>
@@ -3160,13 +3609,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B12" s="24" t="s">
-        <x:v>118</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C12" s="24" t="s">
-        <x:v>119</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D12" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E12" s="24">
         <x:v>2</x:v>
@@ -3178,24 +3627,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H12" s="24" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="I12" s="24">
         <x:v>5</x:v>
       </x:c>
       <x:c r="J12" s="24" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K12" s="25" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="L12" s="25" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="L12" s="43" t="s">
+        <x:v>126</x:v>
       </x:c>
       <x:c r="M12" s="25"/>
       <x:c r="N12" s="25"/>
-      <x:c r="O12" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O12" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P12" s="24"/>
       <x:c r="Q12" s="24"/>
@@ -3213,13 +3662,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="24" t="s">
-        <x:v>122</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C13" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D13" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E13" s="24">
         <x:v>1</x:v>
@@ -3240,15 +3689,15 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="K13" s="25" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="L13" s="25" t="s">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="L13" s="43" t="s">
+        <x:v>129</x:v>
       </x:c>
       <x:c r="M13" s="25"/>
       <x:c r="N13" s="25"/>
-      <x:c r="O13" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O13" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P13" s="24"/>
       <x:c r="Q13" s="24"/>
@@ -3266,13 +3715,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="24" t="s">
-        <x:v>125</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C14" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D14" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E14" s="24">
         <x:v>2</x:v>
@@ -3293,15 +3742,15 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="K14" s="25" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="L14" s="25" t="s">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="L14" s="43" t="s">
+        <x:v>129</x:v>
       </x:c>
       <x:c r="M14" s="25"/>
       <x:c r="N14" s="25"/>
-      <x:c r="O14" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O14" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P14" s="24"/>
       <x:c r="Q14" s="24"/>
@@ -3319,13 +3768,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="24" t="s">
-        <x:v>126</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C15" s="24" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D15" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E15" s="24">
         <x:v>2</x:v>
@@ -3343,18 +3792,18 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J15" s="24" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K15" s="25" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="L15" s="25" t="s">
-        <x:v>128</x:v>
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="L15" s="43" t="s">
+        <x:v>133</x:v>
       </x:c>
       <x:c r="M15" s="25"/>
       <x:c r="N15" s="25"/>
-      <x:c r="O15" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O15" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P15" s="24"/>
       <x:c r="Q15" s="24"/>
@@ -3372,13 +3821,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B16" s="24" t="s">
-        <x:v>129</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C16" s="24" t="s">
-        <x:v>130</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D16" s="24" t="s">
-        <x:v>131</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E16" s="24">
         <x:v>2</x:v>
@@ -3390,7 +3839,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H16" s="24" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="I16" s="24">
         <x:v>5</x:v>
@@ -3399,15 +3848,15 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K16" s="25" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="L16" s="25" t="s">
-        <x:v>133</x:v>
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="L16" s="43" t="s">
+        <x:v>138</x:v>
       </x:c>
       <x:c r="M16" s="25"/>
       <x:c r="N16" s="25"/>
-      <x:c r="O16" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O16" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P16" s="24"/>
       <x:c r="Q16" s="24"/>
@@ -3425,13 +3874,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B17" s="24" t="s">
-        <x:v>134</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C17" s="24" t="s">
-        <x:v>135</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D17" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E17" s="24">
         <x:v>2</x:v>
@@ -3443,24 +3892,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H17" s="24" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="I17" s="24">
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="24" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K17" s="25" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="L17" s="25" t="s">
-        <x:v>136</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="L17" s="43" t="s">
+        <x:v>141</x:v>
       </x:c>
       <x:c r="M17" s="25"/>
       <x:c r="N17" s="25"/>
-      <x:c r="O17" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O17" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P17" s="24"/>
       <x:c r="Q17" s="24"/>
@@ -3484,7 +3933,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="D18" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E18" s="24">
         <x:v>1</x:v>
@@ -3505,15 +3954,15 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="K18" s="25" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="L18" s="25" t="s">
-        <x:v>95</x:v>
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="L18" s="43" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M18" s="25"/>
       <x:c r="N18" s="25"/>
-      <x:c r="O18" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O18" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P18" s="24"/>
       <x:c r="Q18" s="24"/>
@@ -3537,7 +3986,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="D19" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E19" s="24">
         <x:v>1</x:v>
@@ -3558,15 +4007,15 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K19" s="25" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="L19" s="25" t="s">
-        <x:v>139</x:v>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="L19" s="43" t="s">
+        <x:v>144</x:v>
       </x:c>
       <x:c r="M19" s="25"/>
       <x:c r="N19" s="25"/>
-      <x:c r="O19" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O19" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P19" s="24"/>
       <x:c r="Q19" s="24"/>
@@ -3584,13 +4033,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B20" s="24" t="s">
-        <x:v>140</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C20" s="24" t="s">
-        <x:v>141</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D20" s="24" t="s">
-        <x:v>131</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E20" s="24">
         <x:v>2</x:v>
@@ -3608,18 +4057,18 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J20" s="24" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K20" s="25" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="L20" s="25" t="s">
-        <x:v>143</x:v>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="L20" s="43" t="s">
+        <x:v>148</x:v>
       </x:c>
       <x:c r="M20" s="25"/>
       <x:c r="N20" s="25"/>
-      <x:c r="O20" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O20" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P20" s="24"/>
       <x:c r="Q20" s="24"/>
@@ -3637,13 +4086,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B21" s="24" t="s">
-        <x:v>144</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C21" s="24" t="s">
-        <x:v>141</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D21" s="24" t="s">
-        <x:v>131</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E21" s="24">
         <x:v>2</x:v>
@@ -3661,18 +4110,18 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="24" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K21" s="25" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="L21" s="25" t="s">
-        <x:v>143</x:v>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L21" s="43" t="s">
+        <x:v>148</x:v>
       </x:c>
       <x:c r="M21" s="25"/>
       <x:c r="N21" s="25"/>
-      <x:c r="O21" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O21" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P21" s="24"/>
       <x:c r="Q21" s="24"/>
@@ -3690,19 +4139,19 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B22" s="24" t="s">
-        <x:v>146</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C22" s="24" t="s">
-        <x:v>147</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D22" s="24" t="s">
-        <x:v>131</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E22" s="24">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F22" s="24" t="s">
-        <x:v>148</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G22" s="24">
         <x:v>3</x:v>
@@ -3717,15 +4166,15 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K22" s="25" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="L22" s="25" t="s">
-        <x:v>150</x:v>
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="L22" s="43" t="s">
+        <x:v>155</x:v>
       </x:c>
       <x:c r="M22" s="25"/>
       <x:c r="N22" s="25"/>
-      <x:c r="O22" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O22" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P22" s="24"/>
       <x:c r="Q22" s="24"/>
@@ -3743,13 +4192,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B23" s="24" t="s">
-        <x:v>151</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C23" s="24" t="s">
-        <x:v>152</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D23" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E23" s="24">
         <x:v>2</x:v>
@@ -3770,15 +4219,15 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="K23" s="25" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="L23" s="25" t="s">
-        <x:v>154</x:v>
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="L23" s="43" t="s">
+        <x:v>159</x:v>
       </x:c>
       <x:c r="M23" s="25"/>
       <x:c r="N23" s="25"/>
-      <x:c r="O23" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O23" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P23" s="24"/>
       <x:c r="Q23" s="24"/>
@@ -3796,13 +4245,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B24" s="24" t="s">
-        <x:v>155</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C24" s="24" t="s">
-        <x:v>156</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D24" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E24" s="24">
         <x:v>1</x:v>
@@ -3823,15 +4272,15 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="K24" s="25" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="L24" s="25" t="s">
-        <x:v>158</x:v>
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="L24" s="43" t="s">
+        <x:v>163</x:v>
       </x:c>
       <x:c r="M24" s="25"/>
       <x:c r="N24" s="25"/>
-      <x:c r="O24" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O24" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P24" s="24"/>
       <x:c r="Q24" s="24"/>
@@ -3849,13 +4298,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B25" s="24" t="s">
-        <x:v>159</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C25" s="24" t="s">
-        <x:v>156</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D25" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E25" s="24">
         <x:v>2</x:v>
@@ -3876,15 +4325,15 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="K25" s="25" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="L25" s="25" t="s">
-        <x:v>158</x:v>
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="L25" s="43" t="s">
+        <x:v>163</x:v>
       </x:c>
       <x:c r="M25" s="25"/>
       <x:c r="N25" s="25"/>
-      <x:c r="O25" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O25" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P25" s="24"/>
       <x:c r="Q25" s="24"/>
@@ -3902,13 +4351,13 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B26" s="24" t="s">
-        <x:v>160</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C26" s="24" t="s">
-        <x:v>161</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D26" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E26" s="24">
         <x:v>2</x:v>
@@ -3926,18 +4375,18 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J26" s="24" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K26" s="25" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="L26" s="25" t="s">
-        <x:v>164</x:v>
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="L26" s="43" t="s">
+        <x:v>169</x:v>
       </x:c>
       <x:c r="M26" s="25"/>
       <x:c r="N26" s="25"/>
-      <x:c r="O26" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O26" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P26" s="24"/>
       <x:c r="Q26" s="24"/>
@@ -3955,13 +4404,13 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B27" s="24" t="s">
-        <x:v>165</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C27" s="24" t="s">
-        <x:v>166</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D27" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E27" s="24">
         <x:v>1</x:v>
@@ -3979,18 +4428,18 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J27" s="24" t="s">
-        <x:v>167</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="K27" s="25" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="L27" s="25" t="s">
-        <x:v>95</x:v>
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="L27" s="43" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M27" s="25"/>
       <x:c r="N27" s="25"/>
-      <x:c r="O27" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O27" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P27" s="24"/>
       <x:c r="Q27" s="24"/>
@@ -4008,13 +4457,13 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B28" s="24" t="s">
-        <x:v>169</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C28" s="24" t="s">
-        <x:v>170</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D28" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E28" s="24">
         <x:v>2</x:v>
@@ -4026,24 +4475,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H28" s="24" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="I28" s="24">
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="24" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K28" s="25" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="L28" s="25" t="s">
-        <x:v>173</x:v>
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="L28" s="43" t="s">
+        <x:v>178</x:v>
       </x:c>
       <x:c r="M28" s="25"/>
       <x:c r="N28" s="25"/>
-      <x:c r="O28" s="24" t="s">
-        <x:v>174</x:v>
+      <x:c r="O28" s="22" t="s">
+        <x:v>179</x:v>
       </x:c>
       <x:c r="P28" s="24"/>
       <x:c r="Q28" s="24"/>
@@ -4061,19 +4510,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B29" s="24" t="s">
-        <x:v>175</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C29" s="24" t="s">
-        <x:v>176</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D29" s="24" t="s">
-        <x:v>131</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E29" s="24">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F29" s="24" t="s">
-        <x:v>177</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G29" s="24">
         <x:v>3</x:v>
@@ -4088,15 +4537,15 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="K29" s="25" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="L29" s="25" t="s">
-        <x:v>95</x:v>
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="L29" s="43" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M29" s="25"/>
       <x:c r="N29" s="25"/>
-      <x:c r="O29" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O29" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P29" s="24"/>
       <x:c r="Q29" s="24"/>
@@ -4114,13 +4563,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B30" s="24" t="s">
-        <x:v>179</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C30" s="24" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D30" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E30" s="24">
         <x:v>1</x:v>
@@ -4141,15 +4590,15 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K30" s="25" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="L30" s="25" t="s">
-        <x:v>181</x:v>
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="L30" s="43" t="s">
+        <x:v>186</x:v>
       </x:c>
       <x:c r="M30" s="25"/>
       <x:c r="N30" s="25"/>
-      <x:c r="O30" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O30" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P30" s="24"/>
       <x:c r="Q30" s="24"/>
@@ -4167,13 +4616,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B31" s="24" t="s">
-        <x:v>182</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C31" s="24" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D31" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E31" s="24">
         <x:v>2</x:v>
@@ -4194,15 +4643,15 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K31" s="25" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="L31" s="25" t="s">
-        <x:v>181</x:v>
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="L31" s="43" t="s">
+        <x:v>186</x:v>
       </x:c>
       <x:c r="M31" s="25"/>
       <x:c r="N31" s="25"/>
-      <x:c r="O31" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O31" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P31" s="24"/>
       <x:c r="Q31" s="24"/>
@@ -4220,13 +4669,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B32" s="24" t="s">
-        <x:v>184</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C32" s="24" t="s">
-        <x:v>185</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D32" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E32" s="24">
         <x:v>2</x:v>
@@ -4247,15 +4696,15 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K32" s="25" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="L32" s="25" t="s">
-        <x:v>187</x:v>
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="L32" s="43" t="s">
+        <x:v>192</x:v>
       </x:c>
       <x:c r="M32" s="25"/>
       <x:c r="N32" s="25"/>
-      <x:c r="O32" s="24" t="s">
-        <x:v>89</x:v>
+      <x:c r="O32" s="22" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="P32" s="24"/>
       <x:c r="Q32" s="24"/>
@@ -4273,13 +4722,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B33" s="24" t="s">
-        <x:v>188</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C33" s="24" t="s">
-        <x:v>189</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="D33" s="24" t="s">
-        <x:v>131</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E33" s="24">
         <x:v>2</x:v>
@@ -4291,7 +4740,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H33" s="24" t="s">
-        <x:v>190</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="I33" s="24">
         <x:v>5</x:v>
@@ -4300,15 +4749,15 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="K33" s="25" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="L33" s="25" t="s">
-        <x:v>192</x:v>
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="L33" s="43" t="s">
+        <x:v>197</x:v>
       </x:c>
       <x:c r="M33" s="25"/>
       <x:c r="N33" s="25"/>
-      <x:c r="O33" s="24" t="s">
-        <x:v>193</x:v>
+      <x:c r="O33" s="22" t="s">
+        <x:v>198</x:v>
       </x:c>
       <x:c r="P33" s="24"/>
       <x:c r="Q33" s="24"/>
@@ -4326,13 +4775,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B34" s="24" t="s">
-        <x:v>194</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C34" s="24" t="s">
-        <x:v>195</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D34" s="24" t="s">
-        <x:v>131</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E34" s="24">
         <x:v>2</x:v>
@@ -4344,7 +4793,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H34" s="24" t="s">
-        <x:v>196</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I34" s="24">
         <x:v>5</x:v>
@@ -4353,15 +4802,15 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="K34" s="25" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="L34" s="25" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="L34" s="43" t="s">
+        <x:v>203</x:v>
       </x:c>
       <x:c r="M34" s="25"/>
       <x:c r="N34" s="25"/>
-      <x:c r="O34" s="24" t="s">
-        <x:v>199</x:v>
+      <x:c r="O34" s="22" t="s">
+        <x:v>204</x:v>
       </x:c>
       <x:c r="P34" s="24"/>
       <x:c r="Q34" s="24"/>
@@ -4379,13 +4828,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B35" s="24" t="s">
-        <x:v>200</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C35" s="24" t="s">
-        <x:v>201</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D35" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E35" s="24">
         <x:v>1</x:v>
@@ -4403,18 +4852,18 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J35" s="24" t="s">
-        <x:v>202</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="K35" s="25" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="L35" s="25" t="s">
-        <x:v>95</x:v>
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="L35" s="43" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M35" s="25"/>
       <x:c r="N35" s="25"/>
-      <x:c r="O35" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O35" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P35" s="24"/>
       <x:c r="Q35" s="24"/>
@@ -4432,13 +4881,13 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B36" s="24" t="s">
-        <x:v>204</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C36" s="24" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="D36" s="24" t="s">
-        <x:v>131</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E36" s="24">
         <x:v>2</x:v>
@@ -4459,15 +4908,15 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K36" s="25" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="L36" s="25" t="s">
-        <x:v>206</x:v>
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L36" s="43" t="s">
+        <x:v>211</x:v>
       </x:c>
       <x:c r="M36" s="25"/>
       <x:c r="N36" s="25"/>
-      <x:c r="O36" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O36" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P36" s="24"/>
       <x:c r="Q36" s="24"/>
@@ -4485,13 +4934,13 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B37" s="24" t="s">
-        <x:v>207</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C37" s="24" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D37" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E37" s="24">
         <x:v>1</x:v>
@@ -4509,18 +4958,18 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J37" s="24" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K37" s="25" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="L37" s="25" t="s">
-        <x:v>95</x:v>
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="L37" s="43" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M37" s="25"/>
       <x:c r="N37" s="25"/>
-      <x:c r="O37" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O37" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P37" s="24"/>
       <x:c r="Q37" s="24"/>
@@ -4538,19 +4987,19 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B38" s="24" t="s">
-        <x:v>209</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C38" s="24" t="s">
-        <x:v>210</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D38" s="24" t="s">
-        <x:v>211</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E38" s="24">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F38" s="24" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G38" s="24">
         <x:v>4</x:v>
@@ -4565,15 +5014,15 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="K38" s="25" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="L38" s="25" t="s">
-        <x:v>213</x:v>
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="L38" s="43" t="s">
+        <x:v>218</x:v>
       </x:c>
       <x:c r="M38" s="25"/>
       <x:c r="N38" s="25"/>
-      <x:c r="O38" s="24" t="s">
-        <x:v>214</x:v>
+      <x:c r="O38" s="22" t="s">
+        <x:v>219</x:v>
       </x:c>
       <x:c r="P38" s="24"/>
       <x:c r="Q38" s="24"/>
@@ -4591,42 +5040,42 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B39" s="24" t="s">
-        <x:v>215</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C39" s="24" t="s">
-        <x:v>216</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D39" s="24" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E39" s="24">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F39" s="24" t="s">
-        <x:v>177</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G39" s="24">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H39" s="24" t="s">
-        <x:v>217</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="I39" s="24">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J39" s="24" t="s">
-        <x:v>218</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K39" s="25" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="L39" s="25" t="s">
-        <x:v>220</x:v>
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="L39" s="43" t="s">
+        <x:v>225</x:v>
       </x:c>
       <x:c r="M39" s="25"/>
       <x:c r="N39" s="25"/>
-      <x:c r="O39" s="24" t="s">
-        <x:v>96</x:v>
+      <x:c r="O39" s="22" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P39" s="24"/>
       <x:c r="Q39" s="24"/>
@@ -4640,24 +5089,282 @@
       <x:c r="Y39" s="24"/>
     </x:row>
     <x:row r="40">
-      <x:c r="C40" s="20"/>
-      <x:c r="E40" s="20"/>
-      <x:c r="F40" s="20"/>
-      <x:c r="G40" s="20"/>
-      <x:c r="H40" s="20"/>
-      <x:c r="I40" s="20"/>
-      <x:c r="J40" s="20"/>
-      <x:c r="K40" s="20"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="C45" s="20"/>
-      <x:c r="E45" s="20"/>
-      <x:c r="F45" s="20"/>
-      <x:c r="G45" s="20"/>
-      <x:c r="H45" s="20"/>
-      <x:c r="I45" s="20"/>
-      <x:c r="J45" s="20"/>
-      <x:c r="K45" s="20"/>
+      <x:c r="B40" t="str">
+        <x:v>radgrid-son-ogong-gelidus</x:v>
+      </x:c>
+      <x:c r="C40" s="20" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="D40" s="39" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E40" s="20">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F40" s="20" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G40" s="20">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H40" s="20" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I40" s="20">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J40" s="20" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K40" s="20" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="L40" s="40" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="M40" s="41" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="O40" s="39" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="40.5">
+      <x:c r="B41" t="str">
+        <x:v>kal-heron-yeopo-dellons</x:v>
+      </x:c>
+      <x:c r="C41" s="39" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D41" s="39" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E41" s="39">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F41" s="39" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G41" s="39">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H41" s="39" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I41" s="39">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J41" s="39" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="K41" s="40" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="L41" s="42" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="M41" s="39" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="O41" s="39" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="B42" t="str">
+        <x:v>skuld-milia-melkir</x:v>
+      </x:c>
+      <x:c r="C42" s="39" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D42" s="39" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E42" s="39">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F42" s="39" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G42" s="39">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H42" s="39" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I42" s="39">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J42" s="39" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="K42" s="40" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="L42" s="40" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="M42" s="39" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="O42" s="39" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="38.25">
+      <x:c r="B43" t="str">
+        <x:v>landgride-dellons-kyle</x:v>
+      </x:c>
+      <x:c r="C43" s="39" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D43" s="39" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E43" s="39">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F43" s="39" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G43" s="39">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H43" s="39" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="I43" s="39">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J43" s="39" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="K43" s="40" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L43" s="44" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="M43" s="39" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="O43" s="40" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="38.25">
+      <x:c r="B44" t="str">
+        <x:v>branz-bransel-yeopo-dellons</x:v>
+      </x:c>
+      <x:c r="C44" s="39" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="D44" s="39" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E44" s="39">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F44" s="39" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G44" s="39">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H44" s="39" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I44" s="39">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J44" s="39" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="K44" s="40" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="L44" s="44" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="M44" s="39" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="38.25">
+      <x:c r="B45" t="str">
+        <x:v>pie-landgride-dellons</x:v>
+      </x:c>
+      <x:c r="C45" s="20" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D45" s="39" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E45" s="20">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F45" s="20" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G45" s="20">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H45" s="20" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I45" s="20">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J45" s="20" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="K45" s="20" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="L45" s="44" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="M45" s="39" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="O45" s="44" t="s">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="B46" t="str">
+        <x:v>milia-rin-skuld</x:v>
+      </x:c>
+      <x:c r="C46" s="39" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D46" s="39" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E46" s="39">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F46" s="39" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G46" s="39">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H46" s="39" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I46" s="39">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J46" s="39" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K46" s="40" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="M46" s="39" t="s">
+        <x:v>251</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4673,1190 +5380,1190 @@
   <x:sheetData>
     <x:row r="1" ht="15">
       <x:c r="A1" s="9" t="s">
-        <x:v>221</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B1" s="10" t="s">
-        <x:v>222</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C1" s="11" t="s">
-        <x:v>223</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="s">
-        <x:v>224</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B2" s="13" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="C2" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="s">
-        <x:v>225</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B3" s="13" t="s">
-        <x:v>226</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C3" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="s">
-        <x:v>228</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B4" s="13" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C4" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="s">
-        <x:v>230</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B5" s="13" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="C5" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="s">
-        <x:v>231</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B6" s="13" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="C6" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="s">
-        <x:v>233</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B7" s="13" t="s">
-        <x:v>234</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C7" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="s">
-        <x:v>235</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="s">
-        <x:v>236</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="12" t="s">
-        <x:v>237</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="12" t="s">
-        <x:v>238</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
-        <x:v>239</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="12" t="s">
-        <x:v>240</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="12" t="s">
-        <x:v>241</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B13" s="13" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="12" t="s">
-        <x:v>243</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>177</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="12" t="s">
-        <x:v>244</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>245</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B16" s="13" t="s">
-        <x:v>247</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="12" t="s">
-        <x:v>248</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="12" t="s">
-        <x:v>250</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B18" s="13" t="s">
-        <x:v>251</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="12" t="s">
-        <x:v>252</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>253</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="12" t="s">
-        <x:v>254</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B20" s="13" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="12" t="s">
-        <x:v>255</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="12" t="s">
-        <x:v>256</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="12" t="s">
-        <x:v>257</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B23" s="13" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="12" t="s">
-        <x:v>259</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B24" s="13" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="12" t="s">
-        <x:v>260</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B25" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="12" t="s">
-        <x:v>261</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B26" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="12" t="s">
-        <x:v>262</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="12" t="s">
-        <x:v>263</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B28" s="13" t="s">
-        <x:v>264</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="12" t="s">
-        <x:v>265</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C29" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="12" t="s">
-        <x:v>266</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B30" s="13" t="s">
-        <x:v>217</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C30" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="12" t="s">
-        <x:v>267</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>268</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C31" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="12" t="s">
-        <x:v>269</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B32" s="13" t="s">
-        <x:v>270</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C32" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="12" t="s">
-        <x:v>271</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>272</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C33" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="12" t="s">
-        <x:v>273</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B34" s="13" t="s">
-        <x:v>274</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C34" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="12" t="s">
-        <x:v>275</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="C35" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="12" t="s">
-        <x:v>276</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C36" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="C37" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="12" t="s">
-        <x:v>278</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="C38" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="12" t="s">
-        <x:v>279</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B39" s="13" t="s">
-        <x:v>280</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="C39" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="12" t="s">
-        <x:v>281</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>202</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C40" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="12" t="s">
-        <x:v>282</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="C41" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="12" t="s">
-        <x:v>283</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>284</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C42" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="12" t="s">
-        <x:v>285</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>286</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C43" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="12" t="s">
-        <x:v>287</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B44" s="13" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="C44" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="12" t="s">
-        <x:v>288</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B45" s="13" t="s">
-        <x:v>289</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C45" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="12" t="s">
-        <x:v>290</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B46" s="13" t="s">
-        <x:v>190</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C46" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="12" t="s">
-        <x:v>291</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B47" s="13" t="s">
-        <x:v>292</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C47" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="12" t="s">
-        <x:v>293</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B48" s="13" t="s">
-        <x:v>294</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C48" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="12" t="s">
-        <x:v>295</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B49" s="13" t="s">
-        <x:v>296</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C49" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="12" t="s">
-        <x:v>297</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B50" s="13" t="s">
-        <x:v>298</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C50" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="12" t="s">
-        <x:v>299</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B51" s="13" t="s">
-        <x:v>300</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="C51" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="12" t="s">
-        <x:v>301</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B52" s="13" t="s">
-        <x:v>302</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="C52" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B53" s="13" t="s">
-        <x:v>304</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C53" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="12" t="s">
-        <x:v>305</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B54" s="13" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C54" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="12" t="s">
-        <x:v>306</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B55" s="13" t="s">
-        <x:v>307</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C55" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="12" t="s">
-        <x:v>308</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B56" s="13" t="s">
-        <x:v>309</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C56" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="12" t="s">
-        <x:v>310</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B57" s="13" t="s">
-        <x:v>218</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C57" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="12" t="s">
-        <x:v>311</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B58" s="13" t="s">
-        <x:v>312</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C58" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="12" t="s">
-        <x:v>313</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B59" s="13" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C59" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="12" t="s">
-        <x:v>314</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B60" s="13" t="s">
-        <x:v>315</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C60" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="12" t="s">
-        <x:v>316</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B61" s="13" t="s">
-        <x:v>317</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C61" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="12" t="s">
-        <x:v>318</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B62" s="13" t="s">
-        <x:v>319</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="C62" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="12" t="s">
-        <x:v>320</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B63" s="13" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C63" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="12" t="s">
-        <x:v>321</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B64" s="13" t="s">
-        <x:v>322</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C64" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="12" t="s">
-        <x:v>323</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B65" s="13" t="s">
-        <x:v>324</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="C65" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="12" t="s">
-        <x:v>325</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B66" s="13" t="s">
-        <x:v>326</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="C66" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="12" t="s">
-        <x:v>327</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B67" s="13" t="s">
-        <x:v>196</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C67" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="12" t="s">
-        <x:v>328</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B68" s="13" t="s">
-        <x:v>329</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C68" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="12" t="s">
-        <x:v>330</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B69" s="13" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="C69" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="12" t="s">
-        <x:v>331</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B70" s="13" t="s">
-        <x:v>332</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="C70" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="12" t="s">
-        <x:v>333</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B71" s="13" t="s">
-        <x:v>334</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C71" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="12" t="s">
-        <x:v>335</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B72" s="13" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C72" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="12" t="s">
-        <x:v>336</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B73" s="13" t="s">
-        <x:v>337</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C73" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="12" t="s">
-        <x:v>338</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B74" s="13" t="s">
-        <x:v>339</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C74" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="12" t="s">
-        <x:v>340</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B75" s="13" t="s">
-        <x:v>341</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C75" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="12" t="s">
-        <x:v>342</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B76" s="13" t="s">
-        <x:v>343</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C76" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="12" t="s">
-        <x:v>344</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B77" s="13" t="s">
-        <x:v>345</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C77" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="12" t="s">
-        <x:v>346</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B78" s="13" t="s">
-        <x:v>347</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C78" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="12" t="s">
-        <x:v>348</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B79" s="13" t="s">
-        <x:v>349</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C79" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="12" t="s">
-        <x:v>350</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B80" s="13" t="s">
-        <x:v>351</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C80" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="12" t="s">
-        <x:v>352</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B81" s="13" t="s">
-        <x:v>353</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C81" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="12" t="s">
-        <x:v>354</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B82" s="13" t="s">
-        <x:v>355</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="C82" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="12" t="s">
-        <x:v>356</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B83" s="13" t="s">
-        <x:v>357</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C83" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="12" t="s">
-        <x:v>358</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B84" s="13" t="s">
-        <x:v>359</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C84" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="12" t="s">
-        <x:v>360</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B85" s="13" t="s">
-        <x:v>361</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="C85" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="12" t="s">
-        <x:v>362</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B86" s="13" t="s">
-        <x:v>363</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C86" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="12" t="s">
-        <x:v>364</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B87" s="13" t="s">
-        <x:v>365</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="C87" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="12" t="s">
-        <x:v>366</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B88" s="13" t="s">
-        <x:v>367</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="C88" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="12" t="s">
-        <x:v>368</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B89" s="13" t="s">
-        <x:v>369</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C89" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="12" t="s">
-        <x:v>370</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B90" s="13" t="s">
-        <x:v>371</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C90" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="12" t="s">
-        <x:v>372</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B91" s="13" t="s">
-        <x:v>373</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="C91" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="12" t="s">
-        <x:v>374</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B92" s="13" t="s">
-        <x:v>375</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C92" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="12" t="s">
-        <x:v>376</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B93" s="13" t="s">
-        <x:v>377</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C93" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="12" t="s">
-        <x:v>378</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B94" s="13" t="s">
-        <x:v>379</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="C94" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="12" t="s">
-        <x:v>380</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B95" s="13" t="s">
-        <x:v>381</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="C95" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="12" t="s">
-        <x:v>382</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B96" s="13" t="s">
-        <x:v>383</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="C96" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="12" t="s">
-        <x:v>384</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B97" s="13" t="s">
-        <x:v>385</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="C97" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="12" t="s">
-        <x:v>386</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B98" s="13" t="s">
-        <x:v>387</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C98" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="12" t="s">
-        <x:v>388</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B99" s="13" t="s">
-        <x:v>389</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="C99" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="12" t="s">
-        <x:v>390</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B100" s="13" t="s">
-        <x:v>391</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C100" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="12" t="s">
-        <x:v>392</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B101" s="13" t="s">
-        <x:v>393</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="C101" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="12" t="s">
-        <x:v>394</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B102" s="13" t="s">
-        <x:v>395</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="C102" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="12" t="s">
-        <x:v>396</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B103" s="13" t="s">
-        <x:v>397</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="C103" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="12" t="s">
-        <x:v>398</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B104" s="13" t="s">
-        <x:v>399</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="C104" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="12" t="s">
-        <x:v>400</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B105" s="13" t="s">
-        <x:v>401</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="C105" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="12" t="s">
-        <x:v>402</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B106" s="13" t="s">
-        <x:v>403</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="C106" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="12" t="s">
-        <x:v>404</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B107" s="13" t="s">
-        <x:v>405</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C107" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="15" t="s">
-        <x:v>406</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B108" s="16" t="s">
-        <x:v>407</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="C108" s="17" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5868,428 +6575,427 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12" customWidth="1"/>
+    <x:col min="2" max="2" width="18" customWidth="1"/>
+    <x:col min="3" max="3" width="12" customWidth="1"/>
+    <x:col min="4" max="4" width="28" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15">
-      <x:c r="A1" s="38" t="str">
-        <x:v>펫ID</x:v>
-      </x:c>
-      <x:c r="B1" s="38" t="str">
-        <x:v>펫명</x:v>
-      </x:c>
-      <x:c r="C1" s="38" t="str">
-        <x:v>사용여부</x:v>
-      </x:c>
-      <x:c r="D1" s="38" t="str">
-        <x:v>비고</x:v>
+      <x:c r="A1" s="36" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B1" s="36" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="C1" s="36" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D1" s="36" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>p01</x:v>
-      </x:c>
-      <x:c r="B2" s="36" t="str">
-        <x:v>제오</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A2" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="B2" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D2" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>p02</x:v>
-      </x:c>
-      <x:c r="B3" s="36" t="str">
-        <x:v>제브</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A3" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B3" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="C3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D3" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="16.5">
-      <x:c r="A4" t="str">
-        <x:v>p03</x:v>
-      </x:c>
-      <x:c r="B4" s="37" t="str">
-        <x:v>요랑</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A4" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="B4" s="35" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="C4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D4" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>p04</x:v>
-      </x:c>
-      <x:c r="B5" s="36" t="str">
-        <x:v>카람</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A5" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="B5" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="C5" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D5" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="16.5">
-      <x:c r="A6" t="str">
-        <x:v>p05</x:v>
-      </x:c>
-      <x:c r="B6" s="37" t="str">
-        <x:v>유 </x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A6" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="B6" s="35" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="C6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D6" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>p06</x:v>
-      </x:c>
-      <x:c r="B7" s="36" t="str">
-        <x:v>델로</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A7" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B7" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="C7" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D7" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>p07</x:v>
-      </x:c>
-      <x:c r="B8" s="36" t="str">
-        <x:v>리첼</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A8" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B8" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="C8" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>p08</x:v>
-      </x:c>
-      <x:c r="B9" s="36" t="str">
-        <x:v>멜패로</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A9" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B9" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="C9" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D9" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>p09</x:v>
-      </x:c>
-      <x:c r="B10" s="36" t="str">
-        <x:v>파이크</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A10" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="C10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>p10</x:v>
-      </x:c>
-      <x:c r="B11" s="36" t="str">
-        <x:v>루</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A11" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B11" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="C11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D11" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>p11</x:v>
-      </x:c>
-      <x:c r="B12" s="36" t="str">
-        <x:v>연지</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A12" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B12" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="C12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D12" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>p12</x:v>
-      </x:c>
-      <x:c r="B13" s="36" t="str">
-        <x:v>이린</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A13" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="B13" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="C13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D13" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>p13</x:v>
-      </x:c>
-      <x:c r="B14" s="36" t="str">
-        <x:v>크리</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A14" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B14" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D14" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>p14</x:v>
-      </x:c>
-      <x:c r="B15" s="36" t="str">
-        <x:v>윈디</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D15" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A15" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B15" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="C15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D15" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="str">
-        <x:v>p15</x:v>
-      </x:c>
-      <x:c r="B16" s="36" t="str">
-        <x:v>에리</x:v>
-      </x:c>
-      <x:c r="C16" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D16" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A16" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="B16" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="C16" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D16" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>p16</x:v>
-      </x:c>
-      <x:c r="B17" s="36" t="str">
-        <x:v>더지</x:v>
-      </x:c>
-      <x:c r="C17" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A17" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B17" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="C17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D17" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="str">
-        <x:v>p17</x:v>
-      </x:c>
-      <x:c r="B18" s="36" t="str">
-        <x:v>믹</x:v>
-      </x:c>
-      <x:c r="C18" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
-        <x:v>전설</x:v>
+      <x:c r="A18" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="B18" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="C18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D18" t="s">
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" t="str">
-        <x:v>p18</x:v>
-      </x:c>
-      <x:c r="B19" s="36" t="str">
-        <x:v>크로아</x:v>
-      </x:c>
-      <x:c r="C19" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A19" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="B19" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="C19" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D19" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" t="str">
-        <x:v>p19</x:v>
-      </x:c>
-      <x:c r="B20" s="36" t="str">
-        <x:v>파라곤</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A20" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="B20" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="C20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D20" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" t="str">
-        <x:v>p20</x:v>
-      </x:c>
-      <x:c r="B21" s="36" t="str">
-        <x:v>노트</x:v>
-      </x:c>
-      <x:c r="C21" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D21" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A21" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="B21" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="C21" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D21" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>p21</x:v>
-      </x:c>
-      <x:c r="B22" s="36" t="str">
-        <x:v>세리</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A22" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="B22" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="C22" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D22" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" t="str">
-        <x:v>p22</x:v>
-      </x:c>
-      <x:c r="B23" s="36" t="str">
-        <x:v>니키</x:v>
-      </x:c>
-      <x:c r="C23" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D23" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A23" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="B23" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="C23" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D23" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" t="str">
-        <x:v>p23</x:v>
-      </x:c>
-      <x:c r="B24" s="36" t="str">
-        <x:v>니나</x:v>
-      </x:c>
-      <x:c r="C24" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D24" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A24" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B24" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="C24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D24" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" t="str">
-        <x:v>p24</x:v>
-      </x:c>
-      <x:c r="B25" s="36" t="str">
-        <x:v>풍소협</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A25" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="B25" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="C25" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D25" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" t="str">
-        <x:v>p25</x:v>
-      </x:c>
-      <x:c r="B26" s="36" t="str">
-        <x:v>뮤뮤</x:v>
-      </x:c>
-      <x:c r="C26" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A26" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B26" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="C26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D26" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" t="str">
-        <x:v>p26</x:v>
-      </x:c>
-      <x:c r="B27" s="36" t="str">
-        <x:v>이그리트</x:v>
-      </x:c>
-      <x:c r="C27" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D27" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A27" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B27" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="C27" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D27" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" t="str">
-        <x:v>p27</x:v>
-      </x:c>
-      <x:c r="B28" s="36" t="str">
-        <x:v>미믹</x:v>
-      </x:c>
-      <x:c r="C28" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D28" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A28" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="B28" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="C28" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D28" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" t="str">
-        <x:v>p28</x:v>
-      </x:c>
-      <x:c r="B29" s="36" t="str">
-        <x:v>두</x:v>
-      </x:c>
-      <x:c r="C29" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="D29" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A29" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B29" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="C29" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D29" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" t="str">
-        <x:v>p29</x:v>
-      </x:c>
-      <x:c r="B30" s="36" t="str">
-        <x:v>헬레핀</x:v>
-      </x:c>
-      <x:c r="C30"/>
-      <x:c r="D30" t="str">
-        <x:v>희귀</x:v>
+      <x:c r="A30" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="B30" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="D30" t="s">
+        <x:v>471</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
